--- a/data/hachioji_kousei_iryo.xlsx
+++ b/data/hachioji_kousei_iryo.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="[$-411]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
+    <numFmt numFmtId="165" formatCode="0000000"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -48,9 +50,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,11 +424,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>指定自立支援医療機関（育成・更生医療）指定一覧【病院・診療所】（令和8年6月1日現在）</t>
         </is>
       </c>
+      <c r="U1" s="2" t="n"/>
       <c r="AE1" t="inlineStr">
         <is>
           <t>【令和5年7月1日分まで】
@@ -444,7 +449,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
@@ -462,7 +467,7 @@
 辞退</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>医　療　機　関</t>
         </is>
@@ -472,7 +477,7 @@
           <t>開　　設　　者</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>医療の種類</t>
         </is>
@@ -487,7 +492,7 @@
           <t>申請年月日</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>指定年月日</t>
         </is>
@@ -512,7 +517,7 @@
           <t>発番号</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>医療種別</t>
         </is>
@@ -527,12 +532,12 @@
           <t>更生医療</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AC2" s="1" t="inlineStr">
         <is>
           <t>指定年月</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD2" s="1" t="inlineStr">
         <is>
           <t>廃止・
 辞退・
@@ -576,32 +581,32 @@
       </c>
     </row>
     <row r="3">
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>コード</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>コード桁数</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>医科/歯科</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>都13/医1/歯3</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>重複</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>施設毎指定数</t>
         </is>
@@ -616,7 +621,7 @@
           <t>郵便番号</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>区市町村名</t>
         </is>
@@ -626,7 +631,7 @@
           <t>所　在　地</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>電話番号</t>
         </is>
@@ -646,35 +651,35 @@
           <t>所　在　地</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>（みなし指定）</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>2917375</v>
       </c>
       <c r="E4" t="n">
         <v>7</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>1312917375</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -692,7 +697,7 @@
           <t>192-0151</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -702,7 +707,7 @@
           <t>八王子市上川町２１５０</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="1" t="inlineStr">
         <is>
           <t>042-654-4551</t>
         </is>
@@ -722,7 +727,7 @@
           <t>東京都八王子市上川町２１５０</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R4" s="1" t="inlineStr">
         <is>
           <t>10腎臓</t>
         </is>
@@ -735,7 +740,7 @@
       <c r="T4" t="n">
         <v>39114</v>
       </c>
-      <c r="U4" s="1" t="n">
+      <c r="U4" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="V4" t="n">
@@ -749,12 +754,12 @@
       <c r="X4" t="n">
         <v>45748</v>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y4" s="1" t="inlineStr">
         <is>
           <t>7八福障第5985号</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z4" s="1" t="inlineStr">
         <is>
           <t>更生医療</t>
         </is>
@@ -785,28 +790,28 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>2923969</v>
       </c>
       <c r="E5" t="n">
         <v>7</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>1312923969</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -824,7 +829,7 @@
           <t>193-0934</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -834,7 +839,7 @@
           <t>八王子市小比企町１７２２－５</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="1" t="inlineStr">
         <is>
           <t>042-636-1100</t>
         </is>
@@ -854,7 +859,7 @@
           <t>東京都町田市中町１－２３－３</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R5" s="1" t="inlineStr">
         <is>
           <t>10腎臓</t>
         </is>
@@ -867,7 +872,7 @@
       <c r="T5" t="n">
         <v>39111</v>
       </c>
-      <c r="U5" s="1" t="n">
+      <c r="U5" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="V5" t="n">
@@ -881,12 +886,12 @@
       <c r="X5" t="n">
         <v>45748</v>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y5" s="1" t="inlineStr">
         <is>
           <t>6八福障第7389号</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z5" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -907,28 +912,29 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>1-3</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="C6" s="1" t="n"/>
+      <c r="D6" s="3" t="n">
         <v>2924959</v>
       </c>
       <c r="E6" t="n">
         <v>7</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>1312924959</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -946,17 +952,17 @@
           <t>192-0364</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="1" t="inlineStr">
         <is>
           <t>八王子市南大沢２－２　パオレ５階</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="1" t="inlineStr">
         <is>
           <t>042-677-4477</t>
         </is>
@@ -976,12 +982,12 @@
           <t>東京都府中市府中町１－８－１　第７三ツ木ビル</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R6" s="1" t="inlineStr">
         <is>
           <t>10腎臓</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="S6" s="1" t="inlineStr">
         <is>
           <t>松野　裕樹</t>
         </is>
@@ -989,13 +995,13 @@
       <c r="T6" t="n">
         <v>39168</v>
       </c>
-      <c r="U6" s="1" t="n">
+      <c r="U6" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="V6" t="n">
         <v>39173</v>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="W6" s="1" t="inlineStr">
         <is>
           <t>18福保障計第1757号</t>
         </is>
@@ -1003,12 +1009,12 @@
       <c r="X6" t="n">
         <v>45748</v>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y6" s="1" t="inlineStr">
         <is>
           <t>6八福障第6733号</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z6" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -1034,28 +1040,28 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>1-4</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>2930030</v>
       </c>
       <c r="E7" t="n">
         <v>7</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>1312930030</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1073,7 +1079,7 @@
           <t>192-0082</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -1083,7 +1089,7 @@
           <t>八王子市東町７－６　ダヴィンチ八王子７，８階</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="1" t="inlineStr">
         <is>
           <t>042-646-6996</t>
         </is>
@@ -1103,7 +1109,7 @@
           <t>東京都府中市府中町１－８－１　第７三ツ木ビル</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R7" s="1" t="inlineStr">
         <is>
           <t>10腎臓</t>
         </is>
@@ -1116,7 +1122,7 @@
       <c r="T7" t="n">
         <v>39106</v>
       </c>
-      <c r="U7" s="1" t="n">
+      <c r="U7" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="V7" t="n">
@@ -1130,12 +1136,12 @@
       <c r="X7" t="n">
         <v>45748</v>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y7" s="1" t="inlineStr">
         <is>
           <t>6八福障第6732号</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z7" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -1156,28 +1162,28 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>1-5</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>2930345</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>1312930345</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1195,7 +1201,7 @@
           <t>193-0845</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -1205,7 +1211,7 @@
           <t>八王子市初沢町１２７６－１</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" s="1" t="inlineStr">
         <is>
           <t>042-668-0662</t>
         </is>
@@ -1226,7 +1232,7 @@
 ＫＳビル6階</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R8" s="1" t="inlineStr">
         <is>
           <t>10腎臓</t>
         </is>
@@ -1239,7 +1245,7 @@
       <c r="T8" t="n">
         <v>39101</v>
       </c>
-      <c r="U8" s="1" t="n">
+      <c r="U8" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="V8" t="n">
@@ -1253,12 +1259,12 @@
       <c r="X8" t="n">
         <v>45748</v>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y8" s="1" t="inlineStr">
         <is>
           <t>6八福障第7348号</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z8" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -1306,28 +1312,28 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>1-6</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>2927168</v>
       </c>
       <c r="E9" t="n">
         <v>7</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>1312927168</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1345,7 +1351,7 @@
           <t>192-0046</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -1355,7 +1361,7 @@
           <t>八王子市明神町３－２１－１</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N9" s="1" t="inlineStr">
         <is>
           <t>042-660-7887</t>
         </is>
@@ -1375,7 +1381,7 @@
           <t>東京都八王子市明神町３－２１－１</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R9" s="1" t="inlineStr">
         <is>
           <t>10腎臓</t>
         </is>
@@ -1388,7 +1394,7 @@
       <c r="T9" t="n">
         <v>39106</v>
       </c>
-      <c r="U9" s="1" t="n">
+      <c r="U9" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="V9" t="n">
@@ -1402,12 +1408,12 @@
       <c r="X9" t="n">
         <v>45748</v>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y9" s="1" t="inlineStr">
         <is>
           <t>6八福障第6727号</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z9" s="1" t="inlineStr">
         <is>
           <t>更生医療</t>
         </is>
@@ -1423,28 +1429,28 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>1-7</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="3" t="n">
         <v>2927671</v>
       </c>
       <c r="E10" t="n">
         <v>7</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>1312927671</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1462,7 +1468,7 @@
           <t>193-0835</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -1472,7 +1478,7 @@
           <t>八王子市千人町２－１８－１５</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N10" s="1" t="inlineStr">
         <is>
           <t>042-667-2121</t>
         </is>
@@ -1492,7 +1498,7 @@
           <t>東京都八王子市千人町２－１８－１５</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="R10" s="1" t="inlineStr">
         <is>
           <t>10腎臓</t>
         </is>
@@ -1505,7 +1511,7 @@
       <c r="T10" t="n">
         <v>39112</v>
       </c>
-      <c r="U10" s="1" t="n">
+      <c r="U10" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="V10" t="n">
@@ -1519,12 +1525,12 @@
       <c r="X10" t="n">
         <v>45748</v>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y10" s="1" t="inlineStr">
         <is>
           <t>6八福障第6729号</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z10" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -1540,7 +1546,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>1-8</t>
         </is>
@@ -1550,23 +1556,23 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>2930600</v>
       </c>
       <c r="E11" t="n">
         <v>7</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>1312930600</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1584,7 +1590,7 @@
           <t>192-0032</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -1594,7 +1600,7 @@
           <t>八王子市石川町２９６０－５</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N11" s="1" t="inlineStr">
         <is>
           <t>042-643-2701</t>
         </is>
@@ -1614,7 +1620,7 @@
           <t>東京都小平市大沼町２－２－１１</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="R11" s="1" t="inlineStr">
         <is>
           <t>10腎臓</t>
         </is>
@@ -1627,7 +1633,7 @@
       <c r="T11" t="n">
         <v>39111</v>
       </c>
-      <c r="U11" s="1" t="n">
+      <c r="U11" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="V11" t="n">
@@ -1641,12 +1647,12 @@
       <c r="X11" t="n">
         <v>43556</v>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y11" s="1" t="inlineStr">
         <is>
           <t>30八福障収第2448号</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z11" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -1695,28 +1701,28 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>1-9</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="3" t="n">
         <v>2927804</v>
       </c>
       <c r="E12" t="n">
         <v>7</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>1312927804</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1734,7 +1740,7 @@
           <t>192-0916</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -1744,7 +1750,7 @@
           <t>八王子市みなみ野４－１５－７</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="N12" s="1" t="inlineStr">
         <is>
           <t>042-632-8787</t>
         </is>
@@ -1764,7 +1770,7 @@
           <t>東京都八王子市みなみ野４－１５－７</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R12" s="1" t="inlineStr">
         <is>
           <t>10腎臓</t>
         </is>
@@ -1777,7 +1783,7 @@
       <c r="T12" t="n">
         <v>39112</v>
       </c>
-      <c r="U12" s="1" t="n">
+      <c r="U12" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="V12" t="n">
@@ -1791,12 +1797,12 @@
       <c r="X12" t="n">
         <v>45748</v>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y12" s="1" t="inlineStr">
         <is>
           <t>6八福障第6728号</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z12" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -1812,7 +1818,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>1-10</t>
         </is>
@@ -1822,23 +1828,23 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>2927895</v>
       </c>
       <c r="E13" t="n">
         <v>7</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>1312927895</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1856,7 +1862,7 @@
           <t>192-0002</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L13" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -1866,7 +1872,7 @@
           <t>八王子市高月町１１３５</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N13" s="1" t="inlineStr">
         <is>
           <t>042-691-5003</t>
         </is>
@@ -1876,7 +1882,7 @@
           <t>医療法人社団八九十会</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="R13" s="1" t="inlineStr">
         <is>
           <t>05形成外科</t>
         </is>
@@ -1889,7 +1895,7 @@
       <c r="T13" t="n">
         <v>38996</v>
       </c>
-      <c r="U13" s="1" t="n">
+      <c r="U13" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="V13" t="n">
@@ -1900,7 +1906,9 @@
           <t>18福保障計第898号</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="X13" s="1" t="n"/>
+      <c r="Y13" s="1" t="n"/>
+      <c r="Z13" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -1924,28 +1932,29 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>1-11</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="C14" s="1" t="n"/>
+      <c r="D14" s="3" t="n">
         <v>2928638</v>
       </c>
       <c r="E14" t="n">
         <v>7</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>1312928638</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -1953,7 +1962,7 @@
       <c r="I14" t="n">
         <v>2</v>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>医療法人社団主正会　かわさきクリニック</t>
         </is>
@@ -1963,7 +1972,7 @@
           <t>192-0154</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -1973,7 +1982,7 @@
           <t>八王子市下恩方町１１４１－１</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="N14" s="1" t="inlineStr">
         <is>
           <t>042-650-6655</t>
         </is>
@@ -1983,12 +1992,12 @@
           <t>医療法人社団主正会</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="R14" s="1" t="inlineStr">
         <is>
           <t>04整形外科</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="S14" s="1" t="inlineStr">
         <is>
           <t>川﨑　正樹</t>
         </is>
@@ -1996,13 +2005,13 @@
       <c r="T14" t="n">
         <v>39265</v>
       </c>
-      <c r="U14" s="1" t="n">
+      <c r="U14" s="2" t="n">
         <v>39356</v>
       </c>
       <c r="V14" t="n">
         <v>39356</v>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="W14" s="1" t="inlineStr">
         <is>
           <t>19福保障計第696号</t>
         </is>
@@ -2010,12 +2019,12 @@
       <c r="X14" t="n">
         <v>45931</v>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y14" s="1" t="inlineStr">
         <is>
           <t>7八福障第4047号</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z14" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -2036,28 +2045,29 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>1-11</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="C15" s="1" t="n"/>
+      <c r="D15" s="3" t="n">
         <v>2928638</v>
       </c>
       <c r="E15" t="n">
         <v>7</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>1312928638</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>二重</t>
         </is>
@@ -2065,7 +2075,7 @@
       <c r="I15" t="n">
         <v>2</v>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>医療法人社団主正会　かわさきクリニック</t>
         </is>
@@ -2075,7 +2085,7 @@
           <t>192-0154</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -2085,7 +2095,7 @@
           <t>八王子市下恩方町１１４１－１</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N15" s="1" t="inlineStr">
         <is>
           <t>042-650-6655</t>
         </is>
@@ -2100,7 +2110,7 @@
           <t>07脳神経外科</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S15" s="1" t="inlineStr">
         <is>
           <t>川﨑　主税</t>
         </is>
@@ -2108,13 +2118,13 @@
       <c r="T15" t="n">
         <v>39265</v>
       </c>
-      <c r="U15" s="1" t="n">
+      <c r="U15" s="2" t="n">
         <v>39356</v>
       </c>
       <c r="V15" t="n">
         <v>39356</v>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="W15" s="1" t="inlineStr">
         <is>
           <t>19福保障計第696号</t>
         </is>
@@ -2122,12 +2132,12 @@
       <c r="X15" t="n">
         <v>45931</v>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y15" s="1" t="inlineStr">
         <is>
           <t>7八福障第4047号</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z15" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -2148,28 +2158,28 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>1-12</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="3" t="n">
         <v>2928729</v>
       </c>
       <c r="E16" t="n">
         <v>7</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>1312928729</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -2187,7 +2197,7 @@
           <t>193-0833</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L16" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -2197,7 +2207,7 @@
           <t>八王子市めじろ台３－１－１０</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N16" s="1" t="inlineStr">
         <is>
           <t>042-667-8001</t>
         </is>
@@ -2217,7 +2227,7 @@
           <t>東京都八王子市めじろ台３－１－１０</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="R16" s="1" t="inlineStr">
         <is>
           <t>10腎臓</t>
         </is>
@@ -2230,7 +2240,7 @@
       <c r="T16" t="n">
         <v>38994</v>
       </c>
-      <c r="U16" s="1" t="n">
+      <c r="U16" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="V16" t="n">
@@ -2244,12 +2254,12 @@
       <c r="X16" t="n">
         <v>45658</v>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y16" s="1" t="inlineStr">
         <is>
           <t>6八福障第5115号</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z16" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -2270,28 +2280,28 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>1-13</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>2930352</v>
       </c>
       <c r="E17" t="n">
         <v>7</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>1312930352</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -2304,12 +2314,12 @@
           <t>医療法人社団圭徳会　八王子腎クリニック</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" s="1" t="inlineStr">
         <is>
           <t>192-0904</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L17" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -2319,7 +2329,7 @@
           <t>八王子市子安町４－７－１　サザンスカイタワー八王子３階</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N17" s="1" t="inlineStr">
         <is>
           <t>042-620-3377</t>
         </is>
@@ -2340,7 +2350,7 @@
 ＫＳビル6階</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="R17" s="1" t="inlineStr">
         <is>
           <t>10腎臓</t>
         </is>
@@ -2353,7 +2363,7 @@
       <c r="T17" t="n">
         <v>39100</v>
       </c>
-      <c r="U17" s="1" t="n">
+      <c r="U17" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="V17" t="n">
@@ -2367,12 +2377,12 @@
       <c r="X17" t="n">
         <v>45748</v>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y17" s="1" t="inlineStr">
         <is>
           <t>6八福障第7345号</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z17" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -2424,7 +2434,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>1-14</t>
         </is>
@@ -2434,23 +2444,23 @@
           <t>変更（理事長変更）</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>2929057</v>
       </c>
       <c r="E18" t="n">
         <v>7</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>1312929057</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -2463,12 +2473,12 @@
           <t>社会福祉法人日本心身障害児協会　島田療育センターはちおうじ</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" s="1" t="inlineStr">
         <is>
           <t>193-0931</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -2478,7 +2488,7 @@
           <t>八王子市台町４－３３－１３</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N18" s="1" t="inlineStr">
         <is>
           <t>042-634-8511</t>
         </is>
@@ -2498,12 +2508,12 @@
           <t>東京都多摩市中沢１－３１－１</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="R18" s="1" t="inlineStr">
         <is>
           <t>06中枢神経</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S18" s="1" t="inlineStr">
         <is>
           <t>小沢　浩</t>
         </is>
@@ -2511,7 +2521,7 @@
       <c r="T18" t="n">
         <v>40525</v>
       </c>
-      <c r="U18" s="1" t="n">
+      <c r="U18" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="V18" t="n">
@@ -2522,15 +2532,15 @@
           <t>22福保障計第1504号</t>
         </is>
       </c>
-      <c r="X18" s="1" t="n">
+      <c r="X18" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Y18" s="1" t="inlineStr">
         <is>
           <t>4八福障収第1350号</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="Z18" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -2557,28 +2567,28 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>1-15</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>2943827</v>
       </c>
       <c r="E19" t="n">
         <v>7</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>歯科</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>1332943827</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -2596,7 +2606,7 @@
           <t>192-0904</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L19" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -2606,7 +2616,7 @@
           <t>八王子市子安町１－２－８　守屋ビル３階</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N19" s="1" t="inlineStr">
         <is>
           <t>042-656-1631</t>
         </is>
@@ -2626,7 +2636,7 @@
           <t>東京都八王子市大和田町６－２０－６</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="R19" s="1" t="inlineStr">
         <is>
           <t>15歯科矯正</t>
         </is>
@@ -2639,7 +2649,7 @@
       <c r="T19" t="n">
         <v>38991</v>
       </c>
-      <c r="U19" s="1" t="n">
+      <c r="U19" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="V19" t="n">
@@ -2653,12 +2663,12 @@
       <c r="X19" t="n">
         <v>45658</v>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y19" s="1" t="inlineStr">
         <is>
           <t>6八福障第5117号</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="Z19" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -2674,28 +2684,28 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>1-16</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>2945442</v>
       </c>
       <c r="E20" t="n">
         <v>7</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>歯科</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>1332945442</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -2713,7 +2723,7 @@
           <t>192-0904</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L20" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -2723,7 +2733,7 @@
           <t>八王子市子安町４－６－１　Ｐｈｉビル３階</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N20" s="1" t="inlineStr">
         <is>
           <t>042-625-7171</t>
         </is>
@@ -2743,7 +2753,7 @@
           <t>東京都八王子市子安町４－６－１　Ｐｈｉビル３階</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="R20" s="1" t="inlineStr">
         <is>
           <t>15歯科矯正</t>
         </is>
@@ -2756,7 +2766,7 @@
       <c r="T20" t="n">
         <v>39020</v>
       </c>
-      <c r="U20" s="1" t="n">
+      <c r="U20" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="V20" t="n">
@@ -2770,12 +2780,12 @@
       <c r="X20" t="n">
         <v>45658</v>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Y20" s="1" t="inlineStr">
         <is>
           <t>6八福障第5242号</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Z20" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -2791,28 +2801,28 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>1-17</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>2970051</v>
       </c>
       <c r="E21" t="n">
         <v>7</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>1312970051</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -2830,7 +2840,7 @@
           <t>193-0998</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L21" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -2840,7 +2850,7 @@
           <t>八王子市館町１１６３</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N21" s="1" t="inlineStr">
         <is>
           <t>042-665-5611</t>
         </is>
@@ -2860,7 +2870,7 @@
           <t>東京都新宿区新宿６－１－１</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="R21" s="1" t="inlineStr">
         <is>
           <t>01眼科</t>
         </is>
@@ -2873,7 +2883,7 @@
       <c r="T21" t="n">
         <v>39020</v>
       </c>
-      <c r="U21" s="1" t="n">
+      <c r="U21" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="V21" t="n">
@@ -2887,12 +2897,12 @@
       <c r="X21" t="n">
         <v>45658</v>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Y21" s="1" t="inlineStr">
         <is>
           <t>6八福障第5364号</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="Z21" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -2928,28 +2938,28 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>1-17</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="3" t="n">
         <v>2970051</v>
       </c>
       <c r="E22" t="n">
         <v>7</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>1312970051</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>二重</t>
         </is>
@@ -2967,7 +2977,7 @@
           <t>193-0998</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L22" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -2977,7 +2987,7 @@
           <t>八王子市館町１１６３</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N22" s="1" t="inlineStr">
         <is>
           <t>042-665-5611</t>
         </is>
@@ -2997,7 +3007,7 @@
           <t>東京都新宿区新宿６－１－１</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="R22" s="1" t="inlineStr">
         <is>
           <t>02耳鼻咽喉科</t>
         </is>
@@ -3010,7 +3020,7 @@
       <c r="T22" t="n">
         <v>39020</v>
       </c>
-      <c r="U22" s="1" t="n">
+      <c r="U22" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="V22" t="n">
@@ -3024,12 +3034,12 @@
       <c r="X22" t="n">
         <v>45658</v>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Y22" s="1" t="inlineStr">
         <is>
           <t>6八福障第5365号</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z22" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -3065,28 +3075,28 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>1-17</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="3" t="n">
         <v>2970051</v>
       </c>
       <c r="E23" t="n">
         <v>7</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>1312970051</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>二重</t>
         </is>
@@ -3104,7 +3114,7 @@
           <t>193-0998</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L23" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -3114,7 +3124,7 @@
           <t>八王子市館町１１６３</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N23" s="1" t="inlineStr">
         <is>
           <t>042-665-5611</t>
         </is>
@@ -3134,7 +3144,7 @@
           <t>東京都新宿区新宿６－１－１</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="R23" s="1" t="inlineStr">
         <is>
           <t>03口腔</t>
         </is>
@@ -3147,7 +3157,7 @@
       <c r="T23" t="n">
         <v>39020</v>
       </c>
-      <c r="U23" s="1" t="n">
+      <c r="U23" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="V23" t="n">
@@ -3161,12 +3171,12 @@
       <c r="X23" t="n">
         <v>45658</v>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Y23" s="1" t="inlineStr">
         <is>
           <t>6八福障第5366号</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="Z23" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -3192,28 +3202,28 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>1-17</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="3" t="n">
         <v>2970051</v>
       </c>
       <c r="E24" t="n">
         <v>7</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>1312970051</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>二重</t>
         </is>
@@ -3231,7 +3241,7 @@
           <t>193-0998</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L24" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -3241,7 +3251,7 @@
           <t>八王子市館町１１６３</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N24" s="1" t="inlineStr">
         <is>
           <t>042-665-5611</t>
         </is>
@@ -3261,7 +3271,7 @@
           <t>東京都新宿区新宿６－１－１</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="R24" s="1" t="inlineStr">
         <is>
           <t>04整形外科</t>
         </is>
@@ -3274,7 +3284,7 @@
       <c r="T24" t="n">
         <v>39020</v>
       </c>
-      <c r="U24" s="1" t="n">
+      <c r="U24" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="V24" t="n">
@@ -3288,12 +3298,12 @@
       <c r="X24" t="n">
         <v>45658</v>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Y24" s="1" t="inlineStr">
         <is>
           <t>6八福障第5367号</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="Z24" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -3334,28 +3344,28 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>1-17</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="3" t="n">
         <v>2970051</v>
       </c>
       <c r="E25" t="n">
         <v>7</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>1312970051</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>二重</t>
         </is>
@@ -3373,7 +3383,7 @@
           <t>193-0998</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L25" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -3383,7 +3393,7 @@
           <t>八王子市館町１１６３</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N25" s="1" t="inlineStr">
         <is>
           <t>042-665-5611</t>
         </is>
@@ -3403,7 +3413,7 @@
           <t>東京都新宿区新宿６－１－１</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="R25" s="1" t="inlineStr">
         <is>
           <t>05形成外科</t>
         </is>
@@ -3416,7 +3426,7 @@
       <c r="T25" t="n">
         <v>39020</v>
       </c>
-      <c r="U25" s="1" t="n">
+      <c r="U25" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="V25" t="n">
@@ -3430,12 +3440,12 @@
       <c r="X25" t="n">
         <v>45658</v>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Y25" s="1" t="inlineStr">
         <is>
           <t>6八福障第5368号</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="Z25" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -3471,28 +3481,28 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>1-17</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="3" t="n">
         <v>2970051</v>
       </c>
       <c r="E26" t="n">
         <v>7</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>1312970051</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>二重</t>
         </is>
@@ -3510,7 +3520,7 @@
           <t>193-0998</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L26" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -3520,7 +3530,7 @@
           <t>八王子市館町１１６３</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N26" s="1" t="inlineStr">
         <is>
           <t>042-665-5611</t>
         </is>
@@ -3540,7 +3550,7 @@
           <t>東京都新宿区新宿６－１－１</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="R26" s="1" t="inlineStr">
         <is>
           <t>07脳神経外科</t>
         </is>
@@ -3553,7 +3563,7 @@
       <c r="T26" t="n">
         <v>38995</v>
       </c>
-      <c r="U26" s="1" t="n">
+      <c r="U26" s="2" t="n">
         <v>39083</v>
       </c>
       <c r="V26" t="n">
@@ -3567,12 +3577,12 @@
       <c r="X26" t="n">
         <v>45658</v>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Y26" s="1" t="inlineStr">
         <is>
           <t>6八福障第5369号</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="Z26" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -3603,28 +3613,28 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>1-17</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="3" t="n">
         <v>2970051</v>
       </c>
       <c r="E27" t="n">
         <v>7</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>1312970051</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>二重</t>
         </is>
@@ -3642,7 +3652,7 @@
           <t>193-0998</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L27" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -3652,7 +3662,7 @@
           <t>八王子市館町１１６３</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N27" s="1" t="inlineStr">
         <is>
           <t>042-665-5611</t>
         </is>
@@ -3672,7 +3682,7 @@
           <t>東京都新宿区新宿６－１－１</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="R27" s="1" t="inlineStr">
         <is>
           <t>08心臓脈管外科</t>
         </is>
@@ -3685,7 +3695,7 @@
       <c r="T27" t="n">
         <v>39020</v>
       </c>
-      <c r="U27" s="1" t="n">
+      <c r="U27" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="V27" t="n">
@@ -3699,12 +3709,12 @@
       <c r="X27" t="n">
         <v>45658</v>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Y27" s="1" t="inlineStr">
         <is>
           <t>6八福障第5370号</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="Z27" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -3740,28 +3750,28 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>1-17</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="3" t="n">
         <v>2970051</v>
       </c>
       <c r="E28" t="n">
         <v>7</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>1312970051</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>二重</t>
         </is>
@@ -3779,7 +3789,7 @@
           <t>193-0998</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L28" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -3789,7 +3799,7 @@
           <t>八王子市館町１１６３</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N28" s="1" t="inlineStr">
         <is>
           <t>042-665-5611</t>
         </is>
@@ -3809,7 +3819,7 @@
           <t>東京都新宿区新宿６－１－１</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="R28" s="1" t="inlineStr">
         <is>
           <t>10腎臓</t>
         </is>
@@ -3822,7 +3832,7 @@
       <c r="T28" t="n">
         <v>39020</v>
       </c>
-      <c r="U28" s="1" t="n">
+      <c r="U28" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="V28" t="n">
@@ -3836,12 +3846,12 @@
       <c r="X28" t="n">
         <v>45658</v>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Y28" s="1" t="inlineStr">
         <is>
           <t>6八福障第5371号</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="Z28" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -3877,28 +3887,28 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>1-17</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="3" t="n">
         <v>2970051</v>
       </c>
       <c r="E29" t="n">
         <v>7</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>1312970051</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>二重</t>
         </is>
@@ -3916,7 +3926,7 @@
           <t>193-0998</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L29" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -3926,7 +3936,7 @@
           <t>八王子市館町１１６３</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N29" s="1" t="inlineStr">
         <is>
           <t>042-665-5611</t>
         </is>
@@ -3946,7 +3956,7 @@
           <t>東京都新宿区新宿６－１－１</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="R29" s="1" t="inlineStr">
         <is>
           <t>11腎移植</t>
         </is>
@@ -3959,7 +3969,7 @@
       <c r="T29" t="n">
         <v>39020</v>
       </c>
-      <c r="U29" s="1" t="n">
+      <c r="U29" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="V29" t="n">
@@ -3973,12 +3983,12 @@
       <c r="X29" t="n">
         <v>45658</v>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Y29" s="1" t="inlineStr">
         <is>
           <t>6八福障第5372号</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="Z29" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -4014,28 +4024,28 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>1-17</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="3" t="n">
         <v>2970051</v>
       </c>
       <c r="E30" t="n">
         <v>7</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>1312970051</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>二重</t>
         </is>
@@ -4053,7 +4063,7 @@
           <t>193-0998</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L30" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -4063,7 +4073,7 @@
           <t>八王子市館町１１６３</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N30" s="1" t="inlineStr">
         <is>
           <t>042-665-5611</t>
         </is>
@@ -4083,12 +4093,12 @@
           <t>東京都新宿区新宿６－１－１</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="R30" s="1" t="inlineStr">
         <is>
           <t>13-1肝臓移植</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S30" s="1" t="inlineStr">
         <is>
           <t>河地　茂行</t>
         </is>
@@ -4096,7 +4106,7 @@
       <c r="T30" t="n">
         <v>40144</v>
       </c>
-      <c r="U30" s="1" t="n">
+      <c r="U30" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="V30" t="n">
@@ -4107,15 +4117,15 @@
           <t>21福保障計第1081号</t>
         </is>
       </c>
-      <c r="X30" s="1" t="n">
+      <c r="X30" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Y30" s="1" t="inlineStr">
         <is>
           <t>3八福障収第1743号</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="Z30" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -4146,28 +4156,28 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>1-17</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="3" t="n">
         <v>2970051</v>
       </c>
       <c r="E31" t="n">
         <v>7</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>1312970051</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>二重</t>
         </is>
@@ -4185,7 +4195,7 @@
           <t>193-0998</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L31" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -4195,7 +4205,7 @@
           <t>八王子市館町１１６３</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N31" s="1" t="inlineStr">
         <is>
           <t>042-665-5611</t>
         </is>
@@ -4215,7 +4225,7 @@
           <t>東京都新宿区新宿６－１－１</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="R31" s="1" t="inlineStr">
         <is>
           <t>14免疫</t>
         </is>
@@ -4228,7 +4238,7 @@
       <c r="T31" t="n">
         <v>38995</v>
       </c>
-      <c r="U31" s="1" t="n">
+      <c r="U31" s="2" t="n">
         <v>39083</v>
       </c>
       <c r="V31" t="n">
@@ -4242,12 +4252,12 @@
       <c r="X31" t="n">
         <v>45658</v>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Y31" s="1" t="inlineStr">
         <is>
           <t>6八福障第5373号</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Z31" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -4288,33 +4298,33 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>1-18</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="3" t="n">
         <v>2970085</v>
       </c>
       <c r="E32" t="n">
         <v>7</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>1312970085</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -4327,12 +4337,12 @@
           <t>東京都立八王子小児病院</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
         <is>
           <t>193-0931</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L32" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -4352,7 +4362,7 @@
           <t>東京都</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="R32" s="1" t="inlineStr">
         <is>
           <t>12小腸</t>
         </is>
@@ -4365,18 +4375,20 @@
       <c r="T32" t="n">
         <v>39360</v>
       </c>
-      <c r="U32" s="1" t="n">
+      <c r="U32" s="2" t="n">
         <v>39448</v>
       </c>
       <c r="V32" t="n">
         <v>39448</v>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="W32" s="1" t="inlineStr">
         <is>
           <t>19福保障計第1087号</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="X32" s="1" t="n"/>
+      <c r="Y32" s="1" t="n"/>
+      <c r="Z32" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -4400,7 +4412,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>1-18</t>
         </is>
@@ -4410,23 +4422,23 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="3" t="n">
         <v>2970085</v>
       </c>
       <c r="E33" t="n">
         <v>7</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>1312970085</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>二重</t>
         </is>
@@ -4444,7 +4456,7 @@
           <t>193-0931</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L33" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -4454,7 +4466,7 @@
           <t>八王子市台町４－３３－１３</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N33" s="1" t="inlineStr">
         <is>
           <t>042-624-2255</t>
         </is>
@@ -4464,7 +4476,7 @@
           <t>東京都</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="R33" s="1" t="inlineStr">
         <is>
           <t>08心臓脈管外科</t>
         </is>
@@ -4477,7 +4489,7 @@
       <c r="T33" t="n">
         <v>39038</v>
       </c>
-      <c r="U33" s="1" t="n">
+      <c r="U33" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="V33" t="n">
@@ -4488,7 +4500,9 @@
           <t>18福保障計第1220号</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="X33" s="1" t="n"/>
+      <c r="Y33" s="1" t="n"/>
+      <c r="Z33" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -4512,28 +4526,28 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>1-19</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="3" t="n">
         <v>2971232</v>
       </c>
       <c r="E34" t="n">
         <v>7</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>1312971232</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -4551,7 +4565,7 @@
           <t>193-0802</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L34" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -4561,7 +4575,7 @@
           <t>八王子市犬目町６４１</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N34" s="1" t="inlineStr">
         <is>
           <t>042-654-6131</t>
         </is>
@@ -4581,7 +4595,7 @@
           <t>東京都八王子市犬目町６４１</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="R34" s="1" t="inlineStr">
         <is>
           <t>10腎臓</t>
         </is>
@@ -4594,7 +4608,7 @@
       <c r="T34" t="n">
         <v>39115</v>
       </c>
-      <c r="U34" s="1" t="n">
+      <c r="U34" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="V34" t="n">
@@ -4608,12 +4622,12 @@
       <c r="X34" t="n">
         <v>45748</v>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Y34" s="1" t="inlineStr">
         <is>
           <t>6八福障第7351号</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="Z34" s="1" t="inlineStr">
         <is>
           <t>更生医療</t>
         </is>
@@ -4659,28 +4673,28 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="1" t="inlineStr">
         <is>
           <t>1-20</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="3" t="n">
         <v>2971257</v>
       </c>
       <c r="E35" t="n">
         <v>7</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>1312971257</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -4698,7 +4712,7 @@
           <t>192-0042</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L35" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -4708,7 +4722,7 @@
           <t>八王子市中野山王２－１５－１６</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="N35" s="1" t="inlineStr">
         <is>
           <t>042-626-1144</t>
         </is>
@@ -4728,7 +4742,7 @@
           <t>東京都八王子市中野山王２－１５－１６</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="R35" s="1" t="inlineStr">
         <is>
           <t>10腎臓</t>
         </is>
@@ -4741,7 +4755,7 @@
       <c r="T35" t="n">
         <v>39114</v>
       </c>
-      <c r="U35" s="1" t="n">
+      <c r="U35" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="V35" t="n">
@@ -4755,12 +4769,12 @@
       <c r="X35" t="n">
         <v>45748</v>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Y35" s="1" t="inlineStr">
         <is>
           <t>6八福障第7388号</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="Z35" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -4791,28 +4805,28 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>1-21</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="3" t="n">
         <v>2971083</v>
       </c>
       <c r="E36" t="n">
         <v>7</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>1312971083</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -4830,7 +4844,7 @@
           <t>192-0032</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L36" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -4840,7 +4854,7 @@
           <t>八王子市石川町１８３８</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="N36" s="1" t="inlineStr">
         <is>
           <t>042-639-1111</t>
         </is>
@@ -4860,7 +4874,7 @@
           <t>東京都渋谷区富ヶ谷二丁目１０番２号</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="R36" s="1" t="inlineStr">
         <is>
           <t>01眼科</t>
         </is>
@@ -4873,7 +4887,7 @@
       <c r="T36" t="n">
         <v>39009</v>
       </c>
-      <c r="U36" s="1" t="n">
+      <c r="U36" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="V36" t="n">
@@ -4887,12 +4901,12 @@
       <c r="X36" t="n">
         <v>45658</v>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Y36" s="1" t="inlineStr">
         <is>
           <t>6八福障第5678号</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="Z36" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -4933,28 +4947,28 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="1" t="inlineStr">
         <is>
           <t>1-21</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="3" t="n">
         <v>2971083</v>
       </c>
       <c r="E37" t="n">
         <v>7</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>1312971083</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>二重</t>
         </is>
@@ -4972,7 +4986,7 @@
           <t>192-0032</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L37" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -4982,7 +4996,7 @@
           <t xml:space="preserve">八王子市石川町１８３８　</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="N37" s="1" t="inlineStr">
         <is>
           <t>042-639-1111</t>
         </is>
@@ -5002,7 +5016,7 @@
           <t>東京都渋谷区富ヶ谷二丁目１０番２号</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="R37" s="1" t="inlineStr">
         <is>
           <t>02耳鼻咽喉科</t>
         </is>
@@ -5012,7 +5026,7 @@
           <t>山本　光</t>
         </is>
       </c>
-      <c r="U37" s="1" t="n">
+      <c r="U37" s="2" t="n">
         <v>38899</v>
       </c>
       <c r="V37" t="n">
@@ -5031,7 +5045,7 @@
           <t>6八福障第1724号</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
+      <c r="Z37" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -5067,28 +5081,28 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="1" t="inlineStr">
         <is>
           <t>1-21</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="3" t="n">
         <v>2971083</v>
       </c>
       <c r="E38" t="n">
         <v>7</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>1312971083</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>二重</t>
         </is>
@@ -5106,7 +5120,7 @@
           <t>192-0032</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L38" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -5116,7 +5130,7 @@
           <t>八王子市石川町１８３８</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="N38" s="1" t="inlineStr">
         <is>
           <t>042-639-1111</t>
         </is>
@@ -5136,7 +5150,7 @@
           <t>東京都渋谷区富ヶ谷二丁目１０番２号</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="R38" s="1" t="inlineStr">
         <is>
           <t>03口腔</t>
         </is>
@@ -5149,7 +5163,7 @@
       <c r="T38" t="n">
         <v>39009</v>
       </c>
-      <c r="U38" s="1" t="n">
+      <c r="U38" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="V38" t="n">
@@ -5163,12 +5177,12 @@
       <c r="X38" t="n">
         <v>45658</v>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="Y38" s="1" t="inlineStr">
         <is>
           <t>6八福障第5680号</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
+      <c r="Z38" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -5194,28 +5208,28 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="1" t="inlineStr">
         <is>
           <t>1-21</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="3" t="n">
         <v>2971083</v>
       </c>
       <c r="E39" t="n">
         <v>7</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>1312971083</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>二重</t>
         </is>
@@ -5233,7 +5247,7 @@
           <t>192-0032</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="L39" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -5243,7 +5257,7 @@
           <t>八王子市石川町１８３８</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N39" s="1" t="inlineStr">
         <is>
           <t>042-639-1111</t>
         </is>
@@ -5263,7 +5277,7 @@
           <t>東京都渋谷区富ヶ谷二丁目１０番２号</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="R39" s="1" t="inlineStr">
         <is>
           <t>04整形外科</t>
         </is>
@@ -5276,7 +5290,7 @@
       <c r="T39" t="n">
         <v>39009</v>
       </c>
-      <c r="U39" s="1" t="n">
+      <c r="U39" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="V39" t="n">
@@ -5290,12 +5304,12 @@
       <c r="X39" t="n">
         <v>45658</v>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Y39" s="1" t="inlineStr">
         <is>
           <t>6八福障第5682号</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="Z39" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -5341,28 +5355,28 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="1" t="inlineStr">
         <is>
           <t>1-21</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="3" t="n">
         <v>2971083</v>
       </c>
       <c r="E40" t="n">
         <v>7</v>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>1312971083</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>二重</t>
         </is>
@@ -5380,7 +5394,7 @@
           <t>192-0032</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L40" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -5390,7 +5404,7 @@
           <t>八王子市石川町１８３８</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="N40" s="1" t="inlineStr">
         <is>
           <t>042-639-1111</t>
         </is>
@@ -5410,7 +5424,7 @@
           <t>東京都渋谷区富ヶ谷二丁目１０番２号</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="R40" s="1" t="inlineStr">
         <is>
           <t>05形成外科</t>
         </is>
@@ -5423,7 +5437,7 @@
       <c r="T40" t="n">
         <v>39009</v>
       </c>
-      <c r="U40" s="1" t="n">
+      <c r="U40" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="V40" t="n">
@@ -5437,12 +5451,12 @@
       <c r="X40" t="n">
         <v>45658</v>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Y40" s="1" t="inlineStr">
         <is>
           <t>6八福障第5681号</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="Z40" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -5473,28 +5487,28 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="1" t="inlineStr">
         <is>
           <t>1-21</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="3" t="n">
         <v>2971083</v>
       </c>
       <c r="E41" t="n">
         <v>7</v>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>1312971083</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>二重</t>
         </is>
@@ -5512,7 +5526,7 @@
           <t>192-0032</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="L41" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -5522,7 +5536,7 @@
           <t xml:space="preserve">八王子市石川町１８３８　</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="N41" s="1" t="inlineStr">
         <is>
           <t>042-639-1111</t>
         </is>
@@ -5542,7 +5556,7 @@
           <t>東京都渋谷区富ヶ谷二丁目１０番２号</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="R41" s="1" t="inlineStr">
         <is>
           <t>06中枢神経</t>
         </is>
@@ -5552,7 +5566,7 @@
           <t>徳岡　健太郎</t>
         </is>
       </c>
-      <c r="U41" s="1" t="n">
+      <c r="U41" s="2" t="n">
         <v>38899</v>
       </c>
       <c r="V41" t="n">
@@ -5571,7 +5585,7 @@
           <t>6八福障第1291号</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="Z41" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -5592,28 +5606,28 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="1" t="inlineStr">
         <is>
           <t>1-21</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="3" t="n">
         <v>2971083</v>
       </c>
       <c r="E42" t="n">
         <v>7</v>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="3" t="inlineStr">
         <is>
           <t>1312971083</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>二重</t>
         </is>
@@ -5631,7 +5645,7 @@
           <t>192-0032</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L42" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -5641,7 +5655,7 @@
           <t>八王子市石川町１８３８</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="N42" s="1" t="inlineStr">
         <is>
           <t>042-639-1111</t>
         </is>
@@ -5661,7 +5675,7 @@
           <t>東京都渋谷区富ヶ谷二丁目１０番２号</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="R42" s="1" t="inlineStr">
         <is>
           <t>07脳神経外科</t>
         </is>
@@ -5674,7 +5688,7 @@
       <c r="T42" t="n">
         <v>39009</v>
       </c>
-      <c r="U42" s="1" t="n">
+      <c r="U42" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="V42" t="n">
@@ -5688,12 +5702,12 @@
       <c r="X42" t="n">
         <v>45658</v>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Y42" s="1" t="inlineStr">
         <is>
           <t>6八福障第5683号</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="Z42" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -5719,28 +5733,28 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="1" t="inlineStr">
         <is>
           <t>1-21</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="3" t="n">
         <v>2971083</v>
       </c>
       <c r="E43" t="n">
         <v>7</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>1312971083</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>二重</t>
         </is>
@@ -5758,7 +5772,7 @@
           <t>192-0032</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L43" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -5768,7 +5782,7 @@
           <t xml:space="preserve">八王子市石川町１８３８　</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="N43" s="1" t="inlineStr">
         <is>
           <t>042-639-1111</t>
         </is>
@@ -5788,7 +5802,7 @@
           <t>東京都渋谷区富ヶ谷二丁目１０番２号</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="R43" s="1" t="inlineStr">
         <is>
           <t>08心臓脈管外科</t>
         </is>
@@ -5798,7 +5812,7 @@
           <t>西　宏之</t>
         </is>
       </c>
-      <c r="U43" s="1" t="n">
+      <c r="U43" s="2" t="n">
         <v>38899</v>
       </c>
       <c r="V43" t="n">
@@ -5817,7 +5831,7 @@
           <t>6八福障第1800号</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="Z43" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -5853,28 +5867,28 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="1" t="inlineStr">
         <is>
           <t>1-21</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="3" t="n">
         <v>2971083</v>
       </c>
       <c r="E44" t="n">
         <v>7</v>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t>1312971083</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t>二重</t>
         </is>
@@ -5892,7 +5906,7 @@
           <t>192-0032</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L44" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -5902,7 +5916,7 @@
           <t>八王子市石川町１８３８</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="N44" s="1" t="inlineStr">
         <is>
           <t>042-639-1111</t>
         </is>
@@ -5922,7 +5936,7 @@
           <t>東京都渋谷区富ヶ谷二丁目１０番２号</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="R44" s="1" t="inlineStr">
         <is>
           <t>10腎臓</t>
         </is>
@@ -5935,7 +5949,7 @@
       <c r="T44" t="n">
         <v>39009</v>
       </c>
-      <c r="U44" s="1" t="n">
+      <c r="U44" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="V44" t="n">
@@ -5949,12 +5963,12 @@
       <c r="X44" t="n">
         <v>45658</v>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Y44" s="1" t="inlineStr">
         <is>
           <t>6八福障第5679号</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
+      <c r="Z44" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -5990,28 +6004,28 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="1" t="inlineStr">
         <is>
           <t>1-22</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="3" t="n">
         <v>2971141</v>
       </c>
       <c r="E45" t="n">
         <v>7</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>1312971141</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -6029,7 +6043,7 @@
           <t>192-0002</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L45" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -6039,7 +6053,7 @@
           <t>八王子市高月町３６０</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="N45" s="1" t="inlineStr">
         <is>
           <t>042-692-1115</t>
         </is>
@@ -6059,7 +6073,7 @@
           <t>東京都八王子市高月町３６０</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="R45" s="1" t="inlineStr">
         <is>
           <t>04整形外科</t>
         </is>
@@ -6072,7 +6086,7 @@
       <c r="T45" t="n">
         <v>38992</v>
       </c>
-      <c r="U45" s="1" t="n">
+      <c r="U45" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="V45" t="n">
@@ -6086,12 +6100,12 @@
       <c r="X45" t="n">
         <v>45658</v>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Y45" s="1" t="inlineStr">
         <is>
           <t>6八福障第5405号</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="Z45" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -6117,28 +6131,28 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="1" t="inlineStr">
         <is>
           <t>1-22</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="3" t="n">
         <v>2971141</v>
       </c>
       <c r="E46" t="n">
         <v>7</v>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t>1312971141</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>二重</t>
         </is>
@@ -6156,7 +6170,7 @@
           <t>192-0002</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L46" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -6166,7 +6180,7 @@
           <t>八王子市高月町３６０</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="N46" s="1" t="inlineStr">
         <is>
           <t>042-692-1115</t>
         </is>
@@ -6186,7 +6200,7 @@
           <t>東京都八王子市高月町３６０</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="R46" s="1" t="inlineStr">
         <is>
           <t>05形成外科</t>
         </is>
@@ -6199,7 +6213,7 @@
       <c r="T46" t="n">
         <v>38992</v>
       </c>
-      <c r="U46" s="1" t="n">
+      <c r="U46" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="V46" t="n">
@@ -6213,12 +6227,12 @@
       <c r="X46" t="n">
         <v>45658</v>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Y46" s="1" t="inlineStr">
         <is>
           <t>6八福障第5404号</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
+      <c r="Z46" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -6239,28 +6253,28 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="1" t="inlineStr">
         <is>
           <t>1-23</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="3" t="n">
         <v>2971158</v>
       </c>
       <c r="E47" t="n">
         <v>7</v>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>1312971158</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -6278,7 +6292,7 @@
           <t>193-0832</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="L47" s="1" t="inlineStr">
         <is>
           <t>24八王子市</t>
         </is>
@@ -6288,7 +6302,7 @@
           <t>八王子市散田町３－１０－１</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N47" s="1" t="inlineStr">
         <is>
           <t>042-663-0111</t>
         </is>
@@ -6308,7 +6322,7 @@
           <t>東京都八王子市椚田町５８３－１５</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="R47" s="1" t="inlineStr">
         <is>
           <t>10腎臓</t>
         </is>
@@ -6321,7 +6335,7 @@
       <c r="T47" t="n">
         <v>39016</v>
       </c>
-      <c r="U47" s="1" t="n">
+      <c r="U47" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="V47" t="n">
@@ -6335,12 +6349,12 @@
       <c r="X47" t="n">
         <v>45658</v>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Y47" s="1" t="inlineStr">
         <is>
           <t>6八福障第5601号</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
+      <c r="Z47" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -6392,17 +6406,17 @@
       <c r="E48" t="n">
         <v>7</v>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t>1312971018</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -6463,7 +6477,7 @@
       <c r="T48" t="n">
         <v>42241</v>
       </c>
-      <c r="U48" s="1" t="n">
+      <c r="U48" s="2" t="n">
         <v>42278</v>
       </c>
       <c r="V48" t="n">
@@ -6477,7 +6491,7 @@
       <c r="X48" t="n">
         <v>44470</v>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Y48" s="1" t="inlineStr">
         <is>
           <t>3八福障収第645号</t>
         </is>
@@ -6500,7 +6514,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="1" t="inlineStr">
         <is>
           <t>1-25</t>
         </is>
@@ -6511,17 +6525,17 @@
       <c r="E49" t="n">
         <v>7</v>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>1312930097</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -6582,7 +6596,7 @@
       <c r="T49" t="n">
         <v>42513</v>
       </c>
-      <c r="U49" s="1" t="n">
+      <c r="U49" s="2" t="n">
         <v>42552</v>
       </c>
       <c r="V49" t="n">
@@ -6596,7 +6610,7 @@
       <c r="X49" t="n">
         <v>44743</v>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Y49" s="1" t="inlineStr">
         <is>
           <t>4八福障収第282号</t>
         </is>
@@ -6630,17 +6644,17 @@
       <c r="E50" t="n">
         <v>7</v>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>歯科</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>1332947430</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H50" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -6688,7 +6702,7 @@
           <t>神奈川県相模原市緑区下九沢２０３８－１－７２２</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="R50" s="1" t="inlineStr">
         <is>
           <t>15歯科矯正</t>
         </is>
@@ -6701,7 +6715,7 @@
       <c r="T50" t="n">
         <v>42773</v>
       </c>
-      <c r="U50" s="1" t="n">
+      <c r="U50" s="2" t="n">
         <v>42826</v>
       </c>
       <c r="V50" t="n">
@@ -6712,7 +6726,7 @@
           <t>28八福障収第969号</t>
         </is>
       </c>
-      <c r="X50" s="1" t="n">
+      <c r="X50" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="Y50" t="inlineStr">
@@ -6720,7 +6734,7 @@
           <t>4八福障収第1316号</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="Z50" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -6752,17 +6766,17 @@
       <c r="E51" t="n">
         <v>7</v>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>1312930477</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -6810,7 +6824,7 @@
           <t>東京都大田区南六郷一丁目14番11号</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="R51" s="1" t="inlineStr">
         <is>
           <t>10腎臓</t>
         </is>
@@ -6823,7 +6837,7 @@
       <c r="T51" t="n">
         <v>44140</v>
       </c>
-      <c r="U51" s="1" t="n">
+      <c r="U51" s="2" t="n">
         <v>43922</v>
       </c>
       <c r="V51" t="n">
@@ -6834,7 +6848,7 @@
           <t>31八福障収第1058号</t>
         </is>
       </c>
-      <c r="X51" s="1" t="n">
+      <c r="X51" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="Y51" t="inlineStr">
@@ -6842,7 +6856,7 @@
           <t>7八福障第8160号</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
+      <c r="Z51" s="1" t="inlineStr">
         <is>
           <t>育成医療・更生医療</t>
         </is>
@@ -6869,7 +6883,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="1" t="inlineStr">
         <is>
           <t>1-28</t>
         </is>
@@ -6880,17 +6894,17 @@
       <c r="E52" t="n">
         <v>7</v>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="3" t="inlineStr">
         <is>
           <t>1312930766</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -6938,7 +6952,7 @@
           <t>東京都新宿区西新宿３－１２－１２</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="R52" s="1" t="inlineStr">
         <is>
           <t>10腎臓</t>
         </is>
@@ -6951,10 +6965,10 @@
       <c r="T52" t="n">
         <v>44586</v>
       </c>
-      <c r="U52" s="1" t="n">
+      <c r="U52" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="V52" s="1" t="n">
+      <c r="V52" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="W52" t="inlineStr">
@@ -6962,7 +6976,7 @@
           <t>3八福障収第1720号</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
+      <c r="Z52" s="1" t="inlineStr">
         <is>
           <t>更生医療</t>
         </is>
@@ -6987,7 +7001,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="1" t="inlineStr">
         <is>
           <t>1-29</t>
         </is>
@@ -7003,17 +7017,17 @@
       <c r="E53" t="n">
         <v>7</v>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>医科</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>1312971265</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">　</t>
         </is>
@@ -7061,7 +7075,7 @@
           <t>千葉県柏市小青田１－３－１２</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="R53" s="1" t="inlineStr">
         <is>
           <t>10腎臓</t>
         </is>
@@ -7074,10 +7088,10 @@
       <c r="T53" t="n">
         <v>44602</v>
       </c>
-      <c r="U53" s="1" t="n">
+      <c r="U53" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="V53" s="1" t="n">
+      <c r="V53" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="W53" t="inlineStr">
@@ -7085,7 +7099,7 @@
           <t>3八福障収第1553号</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
+      <c r="Z53" s="1" t="inlineStr">
         <is>
           <t>更生医療</t>
         </is>

--- a/data/hachioji_kousei_iryo.xlsx
+++ b/data/hachioji_kousei_iryo.xlsx
@@ -1,24 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\H.H\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h_hyakutake\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6D7F23E-2F99-4B92-BC19-5E450D3E3B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D1821B2-262F-4A76-9A0A-A2B772811D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="13900" xr2:uid="{109B3D45-6C2C-4AAA-AD3E-90420463DC16}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{43C7613F-CFD3-4177-B2A9-F0C2F83E67E0}"/>
   </bookViews>
   <sheets>
     <sheet name="病院・診療所" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">病院・診療所!$A$3:$AJ$54</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">病院・診療所!$A$1:$AK$53</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">病院・診療所!$2:$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">病院・診療所!$A$3:$AK$54</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -41,9 +37,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="497">
-  <si>
-    <t>指定自立支援医療機関（育成・更生医療）指定一覧【病院・診療所】（令和8年6月1日現在）</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="498">
+  <si>
+    <t>指定自立支援医療機関（育成・更生医療）指定一覧【病院・診療所】（令和8年7月1日現在）</t>
     <rPh sb="0" eb="2">
       <t>シテイ</t>
     </rPh>
@@ -2273,16 +2269,6 @@
     <t>1-14</t>
   </si>
   <si>
-    <t>変更（理事長変更）</t>
-    <rPh sb="3" eb="5">
-      <t>リジ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>チョウ</t>
-    </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>社会福祉法人日本心身障害児協会　島田療育センターはちおうじ</t>
     <rPh sb="0" eb="2">
       <t>しゃかい</t>
@@ -3254,7 +3240,7 @@
     <rPh sb="4" eb="5">
       <t>イツ</t>
     </rPh>
-    <phoneticPr fontId="7"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>6八福障第5370号</t>
@@ -3812,6 +3798,10 @@
     <t>1-19</t>
   </si>
   <si>
+    <t>変更（主たる医師)</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
     <t>医療法人社団新山会　希望の丘八王子病院</t>
     <rPh sb="0" eb="2">
       <t>イリョウ</t>
@@ -3887,7 +3877,7 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>工藤　龍彦</t>
+    <t>池田　佐代</t>
     <phoneticPr fontId="4"/>
   </si>
   <si>
@@ -4054,6 +4044,19 @@
   </si>
   <si>
     <t>変更届（開設者氏名：工藤　龍彦→工藤　耕太郎）、変更日：令和8年3月1日</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>変更届（主として担当する医師（工藤　龍彦→池田　佐代、令和8年3月1日）</t>
+    <rPh sb="21" eb="23">
+      <t>イケダ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ヨ</t>
+    </rPh>
     <phoneticPr fontId="4"/>
   </si>
   <si>
@@ -6573,7 +6576,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -6592,7 +6595,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -6607,6 +6610,13 @@
       <sz val="6"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ 明朝"/>
+      <family val="1"/>
       <charset val="128"/>
     </font>
     <font>
@@ -6626,13 +6636,6 @@
       <color indexed="8"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ 明朝"/>
-      <family val="1"/>
       <charset val="128"/>
     </font>
     <font>
@@ -6680,7 +6683,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -6720,43 +6723,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -6770,8 +6736,12 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="double">
         <color indexed="64"/>
       </bottom>
@@ -6822,6 +6792,19 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
@@ -6839,9 +6822,7 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -6859,7 +6840,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6884,7 +6865,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
@@ -6899,10 +6880,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -6914,22 +6895,19 @@
     <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
@@ -6941,61 +6919,64 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="58" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1">
@@ -7022,16 +7003,19 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
@@ -7052,7 +7036,7 @@
     <xf numFmtId="49" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -7064,13 +7048,13 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -7094,55 +7078,55 @@
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="58" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -7157,9 +7141,9 @@
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="標準 2" xfId="1" xr:uid="{C3C6786B-DBF9-4963-91F3-13B9ABB2C918}"/>
-    <cellStyle name="標準_H24.10指定分★(入力用育成更生医療指定一覧H24.7.1締め切り)総合" xfId="3" xr:uid="{490AB0FC-CD9F-45DD-8475-7E7934C5F784}"/>
-    <cellStyle name="標準_医療機関（育成更生）指定一覧" xfId="2" xr:uid="{80A276B1-9336-4E5A-A68B-693AEE684041}"/>
+    <cellStyle name="標準 2" xfId="1" xr:uid="{1C370FB4-4FA3-4477-9354-C27726E054B7}"/>
+    <cellStyle name="標準_H24.10指定分★(入力用育成更生医療指定一覧H24.7.1締め切り)総合" xfId="3" xr:uid="{6045FD4D-BEF9-4B6B-97A0-02CC8856194E}"/>
+    <cellStyle name="標準_医療機関（育成更生）指定一覧" xfId="2" xr:uid="{DA76BD21-CC33-49CE-8127-42C502329B3B}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -7175,9 +7159,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -7185,44 +7169,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -7250,31 +7234,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -7302,26 +7269,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -7330,197 +7280,200 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53D53013-38E1-4022-9C00-29D3B02D46A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{058799E4-6A7C-4015-8521-B2F498E31D46}">
   <dimension ref="A1:AK54"/>
-  <sheetFormatPr defaultRowHeight="18" outlineLevelCol="1" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="13.5" outlineLevelCol="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="7.75" customWidth="1"/>
-    <col min="2" max="2" width="16.75" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="8.25" style="95" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="9" width="10.6640625" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="34.58203125" style="96" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="5.75" style="96" customWidth="1"/>
-    <col min="12" max="12" width="6.75" style="96" customWidth="1"/>
-    <col min="13" max="13" width="32.4140625" style="96" customWidth="1"/>
-    <col min="14" max="14" width="8.25" style="96" customWidth="1"/>
-    <col min="15" max="15" width="24.6640625" style="96" customWidth="1" outlineLevel="1"/>
-    <col min="16" max="16" width="8.25" customWidth="1" outlineLevel="1"/>
-    <col min="17" max="17" width="32.4140625" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="18" width="12.5" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="19" width="12.75" customWidth="1" outlineLevel="1"/>
-    <col min="20" max="20" width="16.5" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="16.5" style="97" customWidth="1"/>
-    <col min="22" max="22" width="16.5" customWidth="1" outlineLevel="1"/>
-    <col min="23" max="23" width="18.75" customWidth="1" outlineLevel="1"/>
-    <col min="24" max="24" width="16.5" customWidth="1" outlineLevel="1"/>
-    <col min="25" max="25" width="18.75" customWidth="1" outlineLevel="1"/>
-    <col min="26" max="26" width="18.75" style="95" customWidth="1"/>
-    <col min="27" max="30" width="8.25" customWidth="1" outlineLevel="1"/>
-    <col min="31" max="36" width="24.83203125" customWidth="1" outlineLevel="1"/>
-    <col min="37" max="37" width="24.83203125" customWidth="1"/>
+    <col min="1" max="1" width="8.5" customWidth="1"/>
+    <col min="2" max="2" width="18.25" customWidth="1" outlineLevel="1"/>
+    <col min="3" max="3" width="9" style="96" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="9" width="11.625" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="37.75" style="97" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="6.25" style="97" customWidth="1"/>
+    <col min="12" max="12" width="7.625" style="97" customWidth="1"/>
+    <col min="13" max="13" width="35.375" style="97" customWidth="1"/>
+    <col min="14" max="14" width="14.375" style="97" customWidth="1"/>
+    <col min="15" max="15" width="26.875" style="97" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="16" width="9" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="17" width="35.375" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="18" width="13.625" customWidth="1"/>
+    <col min="19" max="19" width="13.875" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="20" width="18.375" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="18" style="98" customWidth="1"/>
+    <col min="22" max="22" width="18" customWidth="1" outlineLevel="1"/>
+    <col min="23" max="23" width="20.5" customWidth="1" outlineLevel="1"/>
+    <col min="24" max="24" width="18" customWidth="1" outlineLevel="1"/>
+    <col min="25" max="25" width="20.5" customWidth="1" outlineLevel="1"/>
+    <col min="26" max="26" width="20.5" style="96" customWidth="1"/>
+    <col min="27" max="30" width="9" customWidth="1" outlineLevel="1"/>
+    <col min="31" max="37" width="27.125" customWidth="1" outlineLevel="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="52.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:37" ht="52.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7566,7 +7519,7 @@
       <c r="AI1" s="4"/>
       <c r="AJ1" s="4"/>
     </row>
-    <row r="2" spans="1:37" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:37" ht="21.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>4</v>
       </c>
@@ -7633,98 +7586,98 @@
       <c r="AD2" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="AE2" s="11" t="s">
+      <c r="AE2" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="AF2" s="11" t="s">
+      <c r="AF2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="AG2" s="11" t="s">
+      <c r="AG2" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="AH2" s="11" t="s">
+      <c r="AH2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="AI2" s="11" t="s">
+      <c r="AI2" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="AJ2" s="18" t="s">
+      <c r="AJ2" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="AK2" s="19" t="s">
+      <c r="AK2" s="18" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:37" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="20"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="22" t="s">
+    <row r="3" spans="1:37" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="19"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="23" t="s">
+      <c r="H3" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="I3" s="23" t="s">
+      <c r="I3" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="J3" s="24" t="s">
+      <c r="J3" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="K3" s="24" t="s">
+      <c r="K3" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="L3" s="25" t="s">
+      <c r="L3" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="M3" s="24" t="s">
+      <c r="M3" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="N3" s="25" t="s">
+      <c r="N3" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="O3" s="24" t="s">
+      <c r="O3" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="P3" s="26" t="s">
+      <c r="P3" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="Q3" s="26" t="s">
+      <c r="Q3" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="R3" s="27"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="29" t="s">
+      <c r="R3" s="26"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="V3" s="28"/>
-      <c r="W3" s="28"/>
-      <c r="X3" s="28"/>
-      <c r="Y3" s="28"/>
-      <c r="Z3" s="28"/>
-      <c r="AA3" s="28"/>
-      <c r="AB3" s="28"/>
-      <c r="AC3" s="30"/>
+      <c r="V3" s="27"/>
+      <c r="W3" s="27"/>
+      <c r="X3" s="27"/>
+      <c r="Y3" s="27"/>
+      <c r="Z3" s="19"/>
+      <c r="AA3" s="27"/>
+      <c r="AB3" s="27"/>
+      <c r="AC3" s="29"/>
       <c r="AD3" s="30"/>
-      <c r="AE3" s="27"/>
-      <c r="AF3" s="27"/>
-      <c r="AG3" s="27"/>
-      <c r="AH3" s="27"/>
-      <c r="AI3" s="27"/>
-      <c r="AJ3" s="31"/>
-      <c r="AK3" s="19"/>
+      <c r="AE3" s="20"/>
+      <c r="AF3" s="20"/>
+      <c r="AG3" s="20"/>
+      <c r="AH3" s="20"/>
+      <c r="AI3" s="20"/>
+      <c r="AJ3" s="20"/>
+      <c r="AK3" s="31"/>
     </row>
-    <row r="4" spans="1:37" ht="39.5" thickTop="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:37" ht="41.25" thickTop="1" x14ac:dyDescent="0.15">
       <c r="A4" s="32" t="s">
         <v>41</v>
       </c>
@@ -7828,7 +7781,7 @@
       <c r="AJ4" s="44"/>
       <c r="AK4" s="45"/>
     </row>
-    <row r="5" spans="1:37" ht="39" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:37" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A5" s="46" t="s">
         <v>57</v>
       </c>
@@ -7926,13 +7879,13 @@
       <c r="AH5" s="47"/>
       <c r="AI5" s="54"/>
       <c r="AJ5" s="54"/>
-      <c r="AK5" s="45"/>
+      <c r="AK5" s="55"/>
     </row>
-    <row r="6" spans="1:37" ht="48.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:37" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="55"/>
+      <c r="B6" s="56"/>
       <c r="C6" s="53"/>
       <c r="D6" s="49">
         <v>2924959</v>
@@ -8014,7 +7967,7 @@
       <c r="AB6" s="47">
         <v>1</v>
       </c>
-      <c r="AC6" s="56">
+      <c r="AC6" s="57">
         <v>41904</v>
       </c>
       <c r="AD6" s="47"/>
@@ -8028,13 +7981,13 @@
       <c r="AH6" s="47"/>
       <c r="AI6" s="54"/>
       <c r="AJ6" s="54"/>
-      <c r="AK6" s="45"/>
+      <c r="AK6" s="55"/>
     </row>
-    <row r="7" spans="1:37" ht="52" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:37" ht="54" x14ac:dyDescent="0.15">
       <c r="A7" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="B7" s="55"/>
+      <c r="B7" s="56"/>
       <c r="C7" s="48"/>
       <c r="D7" s="49">
         <v>2930030</v>
@@ -8128,9 +8081,9 @@
       <c r="AH7" s="47"/>
       <c r="AI7" s="54"/>
       <c r="AJ7" s="54"/>
-      <c r="AK7" s="45"/>
+      <c r="AK7" s="55"/>
     </row>
-    <row r="8" spans="1:37" ht="104" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:37" ht="108" x14ac:dyDescent="0.15">
       <c r="A8" s="46" t="s">
         <v>92</v>
       </c>
@@ -8232,19 +8185,19 @@
       <c r="AH8" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="AI8" s="57" t="s">
+      <c r="AI8" s="58" t="s">
         <v>106</v>
       </c>
-      <c r="AJ8" s="57" t="s">
+      <c r="AJ8" s="58" t="s">
         <v>107</v>
       </c>
-      <c r="AK8" s="45"/>
+      <c r="AK8" s="55"/>
     </row>
-    <row r="9" spans="1:37" ht="26" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:37" ht="27" x14ac:dyDescent="0.15">
       <c r="A9" s="46" t="s">
         <v>108</v>
       </c>
-      <c r="B9" s="55"/>
+      <c r="B9" s="56"/>
       <c r="C9" s="48"/>
       <c r="D9" s="49">
         <v>2927168</v>
@@ -8326,7 +8279,7 @@
       <c r="AB9" s="47">
         <v>1</v>
       </c>
-      <c r="AC9" s="56">
+      <c r="AC9" s="57">
         <v>41904</v>
       </c>
       <c r="AD9" s="47"/>
@@ -8336,14 +8289,14 @@
       <c r="AH9" s="47"/>
       <c r="AI9" s="54"/>
       <c r="AJ9" s="54"/>
-      <c r="AK9" s="45"/>
+      <c r="AK9" s="55"/>
     </row>
-    <row r="10" spans="1:37" ht="26" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:37" ht="27" x14ac:dyDescent="0.15">
       <c r="A10" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="58"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="59"/>
       <c r="D10" s="49">
         <v>2927671</v>
       </c>
@@ -8434,13 +8387,13 @@
       <c r="AH10" s="47"/>
       <c r="AI10" s="54"/>
       <c r="AJ10" s="54"/>
-      <c r="AK10" s="45"/>
+      <c r="AK10" s="55"/>
     </row>
-    <row r="11" spans="1:37" ht="65" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:37" ht="67.5" x14ac:dyDescent="0.15">
       <c r="A11" s="46" t="s">
         <v>126</v>
       </c>
-      <c r="B11" s="59"/>
+      <c r="B11" s="60"/>
       <c r="C11" s="48" t="s">
         <v>127</v>
       </c>
@@ -8467,7 +8420,7 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="J11" s="60" t="s">
+      <c r="J11" s="61" t="s">
         <v>128</v>
       </c>
       <c r="K11" s="7" t="s">
@@ -8527,7 +8480,7 @@
       <c r="AC11" s="47">
         <v>41904</v>
       </c>
-      <c r="AD11" s="61">
+      <c r="AD11" s="62">
         <v>50703</v>
       </c>
       <c r="AE11" s="7" t="s">
@@ -8542,19 +8495,19 @@
       <c r="AH11" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="AI11" s="57" t="s">
+      <c r="AI11" s="58" t="s">
         <v>141</v>
       </c>
-      <c r="AJ11" s="57" t="s">
+      <c r="AJ11" s="58" t="s">
         <v>142</v>
       </c>
-      <c r="AK11" s="45"/>
+      <c r="AK11" s="55"/>
     </row>
-    <row r="12" spans="1:37" ht="26" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:37" ht="27" x14ac:dyDescent="0.15">
       <c r="A12" s="46" t="s">
         <v>143</v>
       </c>
-      <c r="B12" s="55"/>
+      <c r="B12" s="56"/>
       <c r="C12" s="48"/>
       <c r="D12" s="49">
         <v>2927804</v>
@@ -8636,7 +8589,7 @@
       <c r="AB12" s="47">
         <v>1</v>
       </c>
-      <c r="AC12" s="56">
+      <c r="AC12" s="57">
         <v>41904</v>
       </c>
       <c r="AD12" s="47"/>
@@ -8646,9 +8599,9 @@
       <c r="AH12" s="47"/>
       <c r="AI12" s="54"/>
       <c r="AJ12" s="54"/>
-      <c r="AK12" s="45"/>
+      <c r="AK12" s="55"/>
     </row>
-    <row r="13" spans="1:37" ht="26" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:37" ht="27" x14ac:dyDescent="0.15">
       <c r="A13" s="46" t="s">
         <v>153</v>
       </c>
@@ -8679,7 +8632,7 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="J13" s="60" t="s">
+      <c r="J13" s="61" t="s">
         <v>155</v>
       </c>
       <c r="K13" s="7" t="s">
@@ -8728,10 +8681,10 @@
       <c r="AB13" s="47">
         <v>1</v>
       </c>
-      <c r="AC13" s="56">
+      <c r="AC13" s="57">
         <v>41901</v>
       </c>
-      <c r="AD13" s="61">
+      <c r="AD13" s="62">
         <v>41903</v>
       </c>
       <c r="AE13" s="7" t="s">
@@ -8742,9 +8695,9 @@
       <c r="AH13" s="47"/>
       <c r="AI13" s="54"/>
       <c r="AJ13" s="54"/>
-      <c r="AK13" s="45"/>
+      <c r="AK13" s="55"/>
     </row>
-    <row r="14" spans="1:37" ht="65" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:37" ht="67.5" x14ac:dyDescent="0.15">
       <c r="A14" s="46" t="s">
         <v>164</v>
       </c>
@@ -8773,7 +8726,7 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="J14" s="62" t="s">
+      <c r="J14" s="63" t="s">
         <v>165</v>
       </c>
       <c r="K14" s="7" t="s">
@@ -8814,7 +8767,7 @@
       <c r="X14" s="52">
         <v>45931</v>
       </c>
-      <c r="Y14" s="63" t="s">
+      <c r="Y14" s="64" t="s">
         <v>173</v>
       </c>
       <c r="Z14" s="53" t="s">
@@ -8826,7 +8779,7 @@
       <c r="AB14" s="47">
         <v>1</v>
       </c>
-      <c r="AC14" s="56">
+      <c r="AC14" s="57">
         <v>41910</v>
       </c>
       <c r="AD14" s="47"/>
@@ -8838,9 +8791,9 @@
       <c r="AH14" s="47"/>
       <c r="AI14" s="54"/>
       <c r="AJ14" s="54"/>
-      <c r="AK14" s="45"/>
+      <c r="AK14" s="55"/>
     </row>
-    <row r="15" spans="1:37" ht="65" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:37" ht="67.5" x14ac:dyDescent="0.15">
       <c r="A15" s="46" t="s">
         <v>164</v>
       </c>
@@ -8869,7 +8822,7 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="J15" s="62" t="s">
+      <c r="J15" s="63" t="s">
         <v>165</v>
       </c>
       <c r="K15" s="7" t="s">
@@ -8892,7 +8845,7 @@
       <c r="R15" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="S15" s="64" t="s">
+      <c r="S15" s="65" t="s">
         <v>177</v>
       </c>
       <c r="T15" s="52">
@@ -8910,7 +8863,7 @@
       <c r="X15" s="52">
         <v>45931</v>
       </c>
-      <c r="Y15" s="63" t="s">
+      <c r="Y15" s="64" t="s">
         <v>173</v>
       </c>
       <c r="Z15" s="53" t="s">
@@ -8922,7 +8875,7 @@
       <c r="AB15" s="47">
         <v>1</v>
       </c>
-      <c r="AC15" s="56">
+      <c r="AC15" s="57">
         <v>41910</v>
       </c>
       <c r="AD15" s="47"/>
@@ -8934,9 +8887,9 @@
       <c r="AH15" s="47"/>
       <c r="AI15" s="54"/>
       <c r="AJ15" s="54"/>
-      <c r="AK15" s="45"/>
+      <c r="AK15" s="55"/>
     </row>
-    <row r="16" spans="1:37" ht="65" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:37" ht="67.5" x14ac:dyDescent="0.15">
       <c r="A16" s="46" t="s">
         <v>178</v>
       </c>
@@ -9022,7 +8975,7 @@
       <c r="AB16" s="47">
         <v>1</v>
       </c>
-      <c r="AC16" s="56">
+      <c r="AC16" s="57">
         <v>41901</v>
       </c>
       <c r="AD16" s="47"/>
@@ -9034,9 +8987,9 @@
       <c r="AH16" s="47"/>
       <c r="AI16" s="54"/>
       <c r="AJ16" s="54"/>
-      <c r="AK16" s="45"/>
+      <c r="AK16" s="55"/>
     </row>
-    <row r="17" spans="1:37" ht="104" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:37" ht="108" x14ac:dyDescent="0.15">
       <c r="A17" s="46" t="s">
         <v>188</v>
       </c>
@@ -9122,7 +9075,7 @@
       <c r="AB17" s="47">
         <v>1</v>
       </c>
-      <c r="AC17" s="56">
+      <c r="AC17" s="57">
         <v>41904</v>
       </c>
       <c r="AD17" s="47"/>
@@ -9138,24 +9091,22 @@
       <c r="AH17" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="AI17" s="57" t="s">
+      <c r="AI17" s="58" t="s">
         <v>199</v>
       </c>
-      <c r="AJ17" s="57" t="s">
+      <c r="AJ17" s="58" t="s">
         <v>200</v>
       </c>
-      <c r="AK17" s="65" t="s">
+      <c r="AK17" s="66" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="18" spans="1:37" ht="39" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:37" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A18" s="46" t="s">
         <v>202</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="C18" s="66"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="67"/>
       <c r="D18" s="49">
         <v>2929057</v>
       </c>
@@ -9180,34 +9131,34 @@
         <v>1</v>
       </c>
       <c r="J18" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="K18" s="50" t="s">
         <v>204</v>
-      </c>
-      <c r="K18" s="50" t="s">
-        <v>205</v>
       </c>
       <c r="L18" s="50" t="s">
         <v>44</v>
       </c>
       <c r="M18" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="N18" s="50" t="s">
         <v>206</v>
       </c>
-      <c r="N18" s="50" t="s">
+      <c r="O18" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="O18" s="7" t="s">
+      <c r="P18" s="51" t="s">
         <v>208</v>
       </c>
-      <c r="P18" s="51" t="s">
+      <c r="Q18" s="51" t="s">
         <v>209</v>
       </c>
-      <c r="Q18" s="51" t="s">
+      <c r="R18" s="50" t="s">
         <v>210</v>
       </c>
-      <c r="R18" s="50" t="s">
+      <c r="S18" s="50" t="s">
         <v>211</v>
-      </c>
-      <c r="S18" s="50" t="s">
-        <v>212</v>
       </c>
       <c r="T18" s="52">
         <v>40525</v>
@@ -9218,14 +9169,14 @@
       <c r="V18" s="52">
         <v>40634</v>
       </c>
-      <c r="W18" s="66" t="s">
-        <v>213</v>
+      <c r="W18" s="67" t="s">
+        <v>212</v>
       </c>
       <c r="X18" s="15">
         <v>45017</v>
       </c>
-      <c r="Y18" s="67" t="s">
-        <v>214</v>
+      <c r="Y18" s="68" t="s">
+        <v>213</v>
       </c>
       <c r="Z18" s="53" t="s">
         <v>67</v>
@@ -9236,25 +9187,25 @@
       <c r="AB18" s="47">
         <v>1</v>
       </c>
-      <c r="AC18" s="56">
+      <c r="AC18" s="57">
         <v>42304</v>
       </c>
       <c r="AD18" s="47"/>
       <c r="AE18" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="AF18" s="7" t="s">
         <v>215</v>
-      </c>
-      <c r="AF18" s="7" t="s">
-        <v>216</v>
       </c>
       <c r="AG18" s="7"/>
       <c r="AH18" s="7"/>
-      <c r="AI18" s="57"/>
+      <c r="AI18" s="58"/>
       <c r="AJ18" s="54"/>
-      <c r="AK18" s="45"/>
+      <c r="AK18" s="55"/>
     </row>
-    <row r="19" spans="1:37" ht="26" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:37" ht="27" x14ac:dyDescent="0.15">
       <c r="A19" s="46" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B19" s="47"/>
       <c r="C19" s="48"/>
@@ -9282,7 +9233,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K19" s="7" t="s">
         <v>190</v>
@@ -9291,25 +9242,25 @@
         <v>44</v>
       </c>
       <c r="M19" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="N19" s="50" t="s">
         <v>219</v>
       </c>
-      <c r="N19" s="50" t="s">
+      <c r="O19" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="O19" s="7" t="s">
+      <c r="P19" s="51" t="s">
         <v>221</v>
       </c>
-      <c r="P19" s="51" t="s">
+      <c r="Q19" s="51" t="s">
         <v>222</v>
       </c>
-      <c r="Q19" s="51" t="s">
+      <c r="R19" s="50" t="s">
         <v>223</v>
       </c>
-      <c r="R19" s="50" t="s">
+      <c r="S19" s="47" t="s">
         <v>224</v>
-      </c>
-      <c r="S19" s="47" t="s">
-        <v>225</v>
       </c>
       <c r="T19" s="52">
         <v>38991</v>
@@ -9321,13 +9272,13 @@
         <v>39083</v>
       </c>
       <c r="W19" s="48" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="X19" s="52">
         <v>45658</v>
       </c>
       <c r="Y19" s="53" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Z19" s="53" t="s">
         <v>67</v>
@@ -9338,7 +9289,7 @@
       <c r="AB19" s="47">
         <v>1</v>
       </c>
-      <c r="AC19" s="56">
+      <c r="AC19" s="57">
         <v>41901</v>
       </c>
       <c r="AD19" s="47"/>
@@ -9348,11 +9299,11 @@
       <c r="AH19" s="47"/>
       <c r="AI19" s="54"/>
       <c r="AJ19" s="54"/>
-      <c r="AK19" s="45"/>
+      <c r="AK19" s="55"/>
     </row>
-    <row r="20" spans="1:37" ht="26" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:37" ht="27" x14ac:dyDescent="0.15">
       <c r="A20" s="46" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B20" s="47"/>
       <c r="C20" s="48"/>
@@ -9380,7 +9331,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K20" s="7" t="s">
         <v>190</v>
@@ -9389,25 +9340,25 @@
         <v>44</v>
       </c>
       <c r="M20" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="N20" s="50" t="s">
         <v>230</v>
       </c>
-      <c r="N20" s="50" t="s">
+      <c r="O20" s="7" t="s">
         <v>231</v>
-      </c>
-      <c r="O20" s="7" t="s">
-        <v>232</v>
       </c>
       <c r="P20" s="51" t="s">
         <v>190</v>
       </c>
       <c r="Q20" s="51" t="s">
+        <v>232</v>
+      </c>
+      <c r="R20" s="50" t="s">
+        <v>223</v>
+      </c>
+      <c r="S20" s="54" t="s">
         <v>233</v>
-      </c>
-      <c r="R20" s="50" t="s">
-        <v>224</v>
-      </c>
-      <c r="S20" s="54" t="s">
-        <v>234</v>
       </c>
       <c r="T20" s="52">
         <v>39020</v>
@@ -9419,13 +9370,13 @@
         <v>39083</v>
       </c>
       <c r="W20" s="48" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="X20" s="52">
         <v>45658</v>
       </c>
       <c r="Y20" s="53" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="Z20" s="53" t="s">
         <v>67</v>
@@ -9436,7 +9387,7 @@
       <c r="AB20" s="47">
         <v>1</v>
       </c>
-      <c r="AC20" s="56">
+      <c r="AC20" s="57">
         <v>41901</v>
       </c>
       <c r="AD20" s="47"/>
@@ -9446,11 +9397,11 @@
       <c r="AH20" s="47"/>
       <c r="AI20" s="54"/>
       <c r="AJ20" s="54"/>
-      <c r="AK20" s="45"/>
+      <c r="AK20" s="55"/>
     </row>
-    <row r="21" spans="1:37" ht="39" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:37" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A21" s="46" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="48"/>
@@ -9478,34 +9429,34 @@
         <v>11</v>
       </c>
       <c r="J21" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="K21" s="7" t="s">
         <v>238</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>239</v>
       </c>
       <c r="L21" s="50" t="s">
         <v>44</v>
       </c>
       <c r="M21" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="N21" s="50" t="s">
         <v>240</v>
       </c>
-      <c r="N21" s="50" t="s">
+      <c r="O21" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="O21" s="7" t="s">
+      <c r="P21" s="51" t="s">
         <v>242</v>
       </c>
-      <c r="P21" s="51" t="s">
+      <c r="Q21" s="51" t="s">
         <v>243</v>
       </c>
-      <c r="Q21" s="51" t="s">
+      <c r="R21" s="50" t="s">
         <v>244</v>
       </c>
-      <c r="R21" s="50" t="s">
+      <c r="S21" s="7" t="s">
         <v>245</v>
-      </c>
-      <c r="S21" s="7" t="s">
-        <v>246</v>
       </c>
       <c r="T21" s="52">
         <v>39020</v>
@@ -9517,13 +9468,13 @@
         <v>39083</v>
       </c>
       <c r="W21" s="48" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="X21" s="52">
         <v>45658</v>
       </c>
       <c r="Y21" s="53" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Z21" s="53" t="s">
         <v>67</v>
@@ -9534,32 +9485,32 @@
       <c r="AB21" s="47">
         <v>1</v>
       </c>
-      <c r="AC21" s="56">
+      <c r="AC21" s="57">
         <v>41901</v>
       </c>
       <c r="AD21" s="47"/>
       <c r="AE21" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="AF21" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="AF21" s="7" t="s">
+      <c r="AG21" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="AG21" s="7" t="s">
+      <c r="AH21" s="7" t="s">
         <v>250</v>
-      </c>
-      <c r="AH21" s="7" t="s">
-        <v>251</v>
       </c>
       <c r="AI21" s="54"/>
       <c r="AJ21" s="54"/>
-      <c r="AK21" s="45"/>
+      <c r="AK21" s="55"/>
     </row>
-    <row r="22" spans="1:37" ht="39" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:37" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A22" s="46" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B22" s="7"/>
-      <c r="C22" s="68"/>
+      <c r="C22" s="69"/>
       <c r="D22" s="49">
         <v>2970051</v>
       </c>
@@ -9584,34 +9535,34 @@
         <v>11</v>
       </c>
       <c r="J22" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="K22" s="7" t="s">
         <v>238</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>239</v>
       </c>
       <c r="L22" s="50" t="s">
         <v>44</v>
       </c>
       <c r="M22" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="N22" s="50" t="s">
+        <v>240</v>
+      </c>
+      <c r="O22" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="P22" s="51" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q22" s="51" t="s">
+        <v>243</v>
+      </c>
+      <c r="R22" s="50" t="s">
         <v>252</v>
       </c>
-      <c r="N22" s="50" t="s">
-        <v>241</v>
-      </c>
-      <c r="O22" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="P22" s="51" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q22" s="51" t="s">
-        <v>244</v>
-      </c>
-      <c r="R22" s="50" t="s">
+      <c r="S22" s="47" t="s">
         <v>253</v>
-      </c>
-      <c r="S22" s="47" t="s">
-        <v>254</v>
       </c>
       <c r="T22" s="52">
         <v>39020</v>
@@ -9623,13 +9574,13 @@
         <v>39083</v>
       </c>
       <c r="W22" s="48" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="X22" s="52">
         <v>45658</v>
       </c>
       <c r="Y22" s="53" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Z22" s="53" t="s">
         <v>67</v>
@@ -9640,29 +9591,29 @@
       <c r="AB22" s="47">
         <v>1</v>
       </c>
-      <c r="AC22" s="56">
+      <c r="AC22" s="57">
         <v>41901</v>
       </c>
       <c r="AD22" s="47"/>
       <c r="AE22" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="AF22" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="AF22" s="7" t="s">
-        <v>257</v>
-      </c>
       <c r="AG22" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="AH22" s="7" t="s">
         <v>250</v>
-      </c>
-      <c r="AH22" s="7" t="s">
-        <v>251</v>
       </c>
       <c r="AI22" s="54"/>
       <c r="AJ22" s="54"/>
-      <c r="AK22" s="45"/>
+      <c r="AK22" s="55"/>
     </row>
-    <row r="23" spans="1:37" ht="39" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:37" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A23" s="46" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="48"/>
@@ -9690,34 +9641,34 @@
         <v>11</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L23" s="50" t="s">
         <v>44</v>
       </c>
       <c r="M23" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="N23" s="50" t="s">
         <v>240</v>
       </c>
-      <c r="N23" s="50" t="s">
+      <c r="O23" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="O23" s="7" t="s">
+      <c r="P23" s="51" t="s">
         <v>242</v>
       </c>
-      <c r="P23" s="51" t="s">
+      <c r="Q23" s="51" t="s">
         <v>243</v>
       </c>
-      <c r="Q23" s="51" t="s">
-        <v>244</v>
-      </c>
       <c r="R23" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="S23" s="54" t="s">
         <v>259</v>
-      </c>
-      <c r="S23" s="54" t="s">
-        <v>260</v>
       </c>
       <c r="T23" s="52">
         <v>39020</v>
@@ -9729,13 +9680,13 @@
         <v>39083</v>
       </c>
       <c r="W23" s="48" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="X23" s="52">
         <v>45658</v>
       </c>
       <c r="Y23" s="53" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Z23" s="53" t="s">
         <v>67</v>
@@ -9751,20 +9702,20 @@
       </c>
       <c r="AD23" s="47"/>
       <c r="AE23" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="AF23" s="7" t="s">
         <v>250</v>
-      </c>
-      <c r="AF23" s="7" t="s">
-        <v>251</v>
       </c>
       <c r="AG23" s="7"/>
       <c r="AH23" s="47"/>
       <c r="AI23" s="54"/>
       <c r="AJ23" s="54"/>
-      <c r="AK23" s="45"/>
+      <c r="AK23" s="55"/>
     </row>
-    <row r="24" spans="1:37" ht="48" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:37" ht="48" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="46" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="48"/>
@@ -9792,34 +9743,34 @@
         <v>11</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L24" s="50" t="s">
         <v>44</v>
       </c>
       <c r="M24" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="N24" s="50" t="s">
         <v>240</v>
       </c>
-      <c r="N24" s="50" t="s">
+      <c r="O24" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="O24" s="7" t="s">
+      <c r="P24" s="51" t="s">
         <v>242</v>
       </c>
-      <c r="P24" s="51" t="s">
+      <c r="Q24" s="51" t="s">
         <v>243</v>
-      </c>
-      <c r="Q24" s="51" t="s">
-        <v>244</v>
       </c>
       <c r="R24" s="50" t="s">
         <v>170</v>
       </c>
       <c r="S24" s="47" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="T24" s="52">
         <v>39020</v>
@@ -9831,13 +9782,13 @@
         <v>39083</v>
       </c>
       <c r="W24" s="48" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="X24" s="52">
         <v>45658</v>
       </c>
       <c r="Y24" s="53" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Z24" s="53" t="s">
         <v>67</v>
@@ -9848,31 +9799,31 @@
       <c r="AB24" s="47">
         <v>1</v>
       </c>
-      <c r="AC24" s="56">
+      <c r="AC24" s="57">
         <v>41901</v>
       </c>
       <c r="AD24" s="47"/>
       <c r="AE24" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="AF24" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="AF24" s="7" t="s">
+      <c r="AG24" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="AG24" s="7" t="s">
-        <v>266</v>
-      </c>
       <c r="AH24" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="AI24" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="AI24" s="7" t="s">
-        <v>251</v>
-      </c>
       <c r="AJ24" s="54"/>
-      <c r="AK24" s="45"/>
+      <c r="AK24" s="55"/>
     </row>
-    <row r="25" spans="1:37" ht="39" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:37" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A25" s="46" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="48"/>
@@ -9900,34 +9851,34 @@
         <v>11</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L25" s="50" t="s">
         <v>44</v>
       </c>
       <c r="M25" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="N25" s="50" t="s">
         <v>240</v>
       </c>
-      <c r="N25" s="50" t="s">
+      <c r="O25" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="O25" s="7" t="s">
+      <c r="P25" s="51" t="s">
         <v>242</v>
       </c>
-      <c r="P25" s="51" t="s">
+      <c r="Q25" s="51" t="s">
         <v>243</v>
-      </c>
-      <c r="Q25" s="51" t="s">
-        <v>244</v>
       </c>
       <c r="R25" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="S25" s="56" t="s">
-        <v>267</v>
+      <c r="S25" s="57" t="s">
+        <v>266</v>
       </c>
       <c r="T25" s="52">
         <v>39020</v>
@@ -9939,13 +9890,13 @@
         <v>39083</v>
       </c>
       <c r="W25" s="48" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="X25" s="52">
         <v>45658</v>
       </c>
       <c r="Y25" s="53" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Z25" s="53" t="s">
         <v>67</v>
@@ -9961,24 +9912,24 @@
       </c>
       <c r="AD25" s="47"/>
       <c r="AE25" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="AF25" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="AF25" s="7" t="s">
-        <v>270</v>
-      </c>
       <c r="AG25" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="AH25" s="7" t="s">
         <v>250</v>
-      </c>
-      <c r="AH25" s="7" t="s">
-        <v>251</v>
       </c>
       <c r="AI25" s="54"/>
       <c r="AJ25" s="54"/>
-      <c r="AK25" s="45"/>
+      <c r="AK25" s="55"/>
     </row>
-    <row r="26" spans="1:37" ht="39" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:37" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A26" s="46" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="48"/>
@@ -10006,34 +9957,34 @@
         <v>11</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L26" s="50" t="s">
+        <v>271</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="N26" s="50" t="s">
+        <v>240</v>
+      </c>
+      <c r="O26" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="P26" s="51" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q26" s="51" t="s">
+        <v>243</v>
+      </c>
+      <c r="R26" s="50" t="s">
         <v>272</v>
       </c>
-      <c r="M26" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="N26" s="50" t="s">
-        <v>241</v>
-      </c>
-      <c r="O26" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="P26" s="51" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q26" s="51" t="s">
-        <v>244</v>
-      </c>
-      <c r="R26" s="50" t="s">
+      <c r="S26" s="7" t="s">
         <v>273</v>
-      </c>
-      <c r="S26" s="7" t="s">
-        <v>274</v>
       </c>
       <c r="T26" s="52">
         <v>38995</v>
@@ -10045,13 +9996,13 @@
         <v>39083</v>
       </c>
       <c r="W26" s="48" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="X26" s="52">
         <v>45658</v>
       </c>
       <c r="Y26" s="53" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Z26" s="53" t="s">
         <v>67</v>
@@ -10062,27 +10013,27 @@
       <c r="AB26" s="47">
         <v>1</v>
       </c>
-      <c r="AC26" s="56">
+      <c r="AC26" s="57">
         <v>41901</v>
       </c>
       <c r="AD26" s="47"/>
       <c r="AE26" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AF26" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="AG26" s="7" t="s">
         <v>250</v>
-      </c>
-      <c r="AG26" s="7" t="s">
-        <v>251</v>
       </c>
       <c r="AH26" s="47"/>
       <c r="AI26" s="54"/>
       <c r="AJ26" s="54"/>
-      <c r="AK26" s="45"/>
+      <c r="AK26" s="55"/>
     </row>
-    <row r="27" spans="1:37" ht="39" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:37" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A27" s="46" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="48"/>
@@ -10110,34 +10061,34 @@
         <v>11</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L27" s="50" t="s">
         <v>44</v>
       </c>
       <c r="M27" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="N27" s="50" t="s">
         <v>240</v>
       </c>
-      <c r="N27" s="50" t="s">
+      <c r="O27" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="O27" s="7" t="s">
+      <c r="P27" s="51" t="s">
         <v>242</v>
       </c>
-      <c r="P27" s="51" t="s">
+      <c r="Q27" s="51" t="s">
         <v>243</v>
       </c>
-      <c r="Q27" s="51" t="s">
-        <v>244</v>
-      </c>
       <c r="R27" s="50" t="s">
+        <v>277</v>
+      </c>
+      <c r="S27" s="70" t="s">
         <v>278</v>
-      </c>
-      <c r="S27" s="69" t="s">
-        <v>279</v>
       </c>
       <c r="T27" s="52">
         <v>39020</v>
@@ -10149,13 +10100,13 @@
         <v>39083</v>
       </c>
       <c r="W27" s="48" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="X27" s="52">
         <v>45658</v>
       </c>
       <c r="Y27" s="53" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Z27" s="53" t="s">
         <v>67</v>
@@ -10171,24 +10122,24 @@
       </c>
       <c r="AD27" s="47"/>
       <c r="AE27" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="AF27" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="AF27" s="7" t="s">
-        <v>282</v>
-      </c>
       <c r="AG27" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="AH27" s="7" t="s">
         <v>250</v>
-      </c>
-      <c r="AH27" s="7" t="s">
-        <v>251</v>
       </c>
       <c r="AI27" s="54"/>
       <c r="AJ27" s="54"/>
-      <c r="AK27" s="45"/>
+      <c r="AK27" s="55"/>
     </row>
-    <row r="28" spans="1:37" ht="39" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:37" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A28" s="46" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="48"/>
@@ -10216,34 +10167,34 @@
         <v>11</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L28" s="50" t="s">
         <v>44</v>
       </c>
       <c r="M28" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="N28" s="50" t="s">
         <v>240</v>
       </c>
-      <c r="N28" s="50" t="s">
+      <c r="O28" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="O28" s="7" t="s">
-        <v>242</v>
-      </c>
       <c r="P28" s="51" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Q28" s="51" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="R28" s="50" t="s">
         <v>50</v>
       </c>
       <c r="S28" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="T28" s="52">
         <v>39020</v>
@@ -10255,13 +10206,13 @@
         <v>39083</v>
       </c>
       <c r="W28" s="48" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="X28" s="52">
         <v>45658</v>
       </c>
       <c r="Y28" s="53" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Z28" s="53" t="s">
         <v>67</v>
@@ -10277,24 +10228,24 @@
       </c>
       <c r="AD28" s="47"/>
       <c r="AE28" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="AF28" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="AF28" s="7" t="s">
-        <v>287</v>
-      </c>
       <c r="AG28" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="AH28" s="7" t="s">
         <v>250</v>
-      </c>
-      <c r="AH28" s="7" t="s">
-        <v>251</v>
       </c>
       <c r="AI28" s="54"/>
       <c r="AJ28" s="54"/>
-      <c r="AK28" s="45"/>
+      <c r="AK28" s="55"/>
     </row>
-    <row r="29" spans="1:37" ht="39" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:37" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A29" s="46" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="48"/>
@@ -10322,34 +10273,34 @@
         <v>11</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L29" s="50" t="s">
         <v>44</v>
       </c>
       <c r="M29" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="N29" s="50" t="s">
         <v>240</v>
       </c>
-      <c r="N29" s="50" t="s">
+      <c r="O29" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="O29" s="7" t="s">
+      <c r="P29" s="51" t="s">
         <v>242</v>
       </c>
-      <c r="P29" s="51" t="s">
+      <c r="Q29" s="51" t="s">
         <v>243</v>
       </c>
-      <c r="Q29" s="51" t="s">
-        <v>244</v>
-      </c>
       <c r="R29" s="50" t="s">
+        <v>287</v>
+      </c>
+      <c r="S29" s="47" t="s">
         <v>288</v>
-      </c>
-      <c r="S29" s="47" t="s">
-        <v>289</v>
       </c>
       <c r="T29" s="52">
         <v>39020</v>
@@ -10361,13 +10312,13 @@
         <v>39083</v>
       </c>
       <c r="W29" s="48" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="X29" s="52">
         <v>45658</v>
       </c>
       <c r="Y29" s="53" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Z29" s="53" t="s">
         <v>67</v>
@@ -10378,29 +10329,29 @@
       <c r="AB29" s="47">
         <v>1</v>
       </c>
-      <c r="AC29" s="56">
+      <c r="AC29" s="57">
         <v>41901</v>
       </c>
       <c r="AD29" s="47"/>
       <c r="AE29" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AF29" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG29" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="AH29" s="7" t="s">
         <v>250</v>
-      </c>
-      <c r="AH29" s="7" t="s">
-        <v>251</v>
       </c>
       <c r="AI29" s="54"/>
       <c r="AJ29" s="54"/>
-      <c r="AK29" s="45"/>
+      <c r="AK29" s="55"/>
     </row>
-    <row r="30" spans="1:37" ht="39" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:37" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A30" s="46" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="48"/>
@@ -10428,52 +10379,52 @@
         <v>11</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K30" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L30" s="50" t="s">
         <v>44</v>
       </c>
       <c r="M30" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="N30" s="50" t="s">
         <v>240</v>
       </c>
-      <c r="N30" s="50" t="s">
+      <c r="O30" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="O30" s="7" t="s">
-        <v>242</v>
-      </c>
       <c r="P30" s="51" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Q30" s="51" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="R30" s="50" t="s">
+        <v>291</v>
+      </c>
+      <c r="S30" s="71" t="s">
         <v>292</v>
-      </c>
-      <c r="S30" s="70" t="s">
-        <v>293</v>
       </c>
       <c r="T30" s="52">
         <v>40144</v>
       </c>
-      <c r="U30" s="71">
+      <c r="U30" s="72">
         <v>40269</v>
       </c>
-      <c r="V30" s="72">
+      <c r="V30" s="73">
         <v>40269</v>
       </c>
-      <c r="W30" s="66" t="s">
-        <v>294</v>
+      <c r="W30" s="67" t="s">
+        <v>293</v>
       </c>
       <c r="X30" s="15">
         <v>44652</v>
       </c>
-      <c r="Y30" s="73" t="s">
-        <v>295</v>
+      <c r="Y30" s="74" t="s">
+        <v>294</v>
       </c>
       <c r="Z30" s="53" t="s">
         <v>67</v>
@@ -10488,23 +10439,23 @@
         <v>42204</v>
       </c>
       <c r="AD30" s="47"/>
-      <c r="AE30" s="74" t="s">
-        <v>296</v>
+      <c r="AE30" s="75" t="s">
+        <v>295</v>
       </c>
       <c r="AF30" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="AG30" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="AG30" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="AH30" s="69"/>
+      <c r="AH30" s="70"/>
       <c r="AI30" s="54"/>
       <c r="AJ30" s="54"/>
-      <c r="AK30" s="45"/>
+      <c r="AK30" s="55"/>
     </row>
-    <row r="31" spans="1:37" ht="39" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:37" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A31" s="46" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="48"/>
@@ -10532,34 +10483,34 @@
         <v>11</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L31" s="50" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M31" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="N31" s="50" t="s">
         <v>240</v>
       </c>
-      <c r="N31" s="50" t="s">
+      <c r="O31" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="O31" s="7" t="s">
-        <v>242</v>
-      </c>
       <c r="P31" s="51" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Q31" s="51" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="R31" s="50" t="s">
+        <v>296</v>
+      </c>
+      <c r="S31" s="47" t="s">
         <v>297</v>
-      </c>
-      <c r="S31" s="47" t="s">
-        <v>298</v>
       </c>
       <c r="T31" s="52">
         <v>38995</v>
@@ -10571,13 +10522,13 @@
         <v>39083</v>
       </c>
       <c r="W31" s="48" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="X31" s="52">
         <v>45658</v>
       </c>
       <c r="Y31" s="53" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Z31" s="53" t="s">
         <v>67</v>
@@ -10588,34 +10539,34 @@
       <c r="AB31" s="47">
         <v>1</v>
       </c>
-      <c r="AC31" s="56">
+      <c r="AC31" s="57">
         <v>41901</v>
       </c>
       <c r="AD31" s="47"/>
       <c r="AE31" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="AF31" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="AF31" s="7" t="s">
+      <c r="AG31" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="AG31" s="7" t="s">
+      <c r="AH31" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="AI31" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="AJ31" s="54"/>
+      <c r="AK31" s="55"/>
+    </row>
+    <row r="32" spans="1:37" ht="148.5" x14ac:dyDescent="0.15">
+      <c r="A32" s="46" t="s">
         <v>302</v>
       </c>
-      <c r="AH31" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="AI31" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="AJ31" s="54"/>
-      <c r="AK31" s="45"/>
-    </row>
-    <row r="32" spans="1:37" ht="143" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="46" t="s">
-        <v>303</v>
-      </c>
       <c r="B32" s="47"/>
-      <c r="C32" s="75" t="s">
+      <c r="C32" s="76" t="s">
         <v>154</v>
       </c>
       <c r="D32" s="49">
@@ -10641,47 +10592,47 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="J32" s="60" t="s">
-        <v>304</v>
+      <c r="J32" s="61" t="s">
+        <v>303</v>
       </c>
       <c r="K32" s="49" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L32" s="50" t="s">
         <v>44</v>
       </c>
       <c r="M32" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="N32" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="N32" s="7" t="s">
+      <c r="O32" s="7" t="s">
         <v>306</v>
-      </c>
-      <c r="O32" s="7" t="s">
-        <v>307</v>
       </c>
       <c r="P32" s="51"/>
       <c r="Q32" s="51"/>
       <c r="R32" s="50" t="s">
+        <v>307</v>
+      </c>
+      <c r="S32" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="S32" s="7" t="s">
+      <c r="T32" s="77">
+        <v>39360</v>
+      </c>
+      <c r="U32" s="78">
+        <v>39448</v>
+      </c>
+      <c r="V32" s="77">
+        <v>39448</v>
+      </c>
+      <c r="W32" s="76" t="s">
         <v>309</v>
       </c>
-      <c r="T32" s="76">
-        <v>39360</v>
-      </c>
-      <c r="U32" s="77">
-        <v>39448</v>
-      </c>
-      <c r="V32" s="76">
-        <v>39448</v>
-      </c>
-      <c r="W32" s="75" t="s">
-        <v>310</v>
-      </c>
-      <c r="X32" s="75"/>
-      <c r="Y32" s="75"/>
-      <c r="Z32" s="75" t="s">
+      <c r="X32" s="76"/>
+      <c r="Y32" s="76"/>
+      <c r="Z32" s="76" t="s">
         <v>67</v>
       </c>
       <c r="AA32" s="47">
@@ -10690,25 +10641,25 @@
       <c r="AB32" s="47">
         <v>1</v>
       </c>
-      <c r="AC32" s="56">
+      <c r="AC32" s="57">
         <v>42001</v>
       </c>
       <c r="AD32" s="47">
         <v>42202</v>
       </c>
       <c r="AE32" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AF32" s="7"/>
       <c r="AG32" s="7"/>
       <c r="AH32" s="47"/>
       <c r="AI32" s="54"/>
       <c r="AJ32" s="54"/>
-      <c r="AK32" s="45"/>
+      <c r="AK32" s="55"/>
     </row>
-    <row r="33" spans="1:37" ht="143" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:37" ht="148.5" x14ac:dyDescent="0.15">
       <c r="A33" s="46" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B33" s="47"/>
       <c r="C33" s="48" t="s">
@@ -10737,31 +10688,31 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="J33" s="60" t="s">
-        <v>312</v>
+      <c r="J33" s="61" t="s">
+        <v>311</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L33" s="50" t="s">
         <v>44</v>
       </c>
       <c r="M33" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="N33" s="50" t="s">
+        <v>305</v>
+      </c>
+      <c r="O33" s="7" t="s">
         <v>306</v>
-      </c>
-      <c r="O33" s="7" t="s">
-        <v>307</v>
       </c>
       <c r="P33" s="51"/>
       <c r="Q33" s="51"/>
       <c r="R33" s="50" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="S33" s="47" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="T33" s="52">
         <v>39038</v>
@@ -10773,7 +10724,7 @@
         <v>39083</v>
       </c>
       <c r="W33" s="48" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="X33" s="53"/>
       <c r="Y33" s="53"/>
@@ -10786,27 +10737,29 @@
       <c r="AB33" s="47">
         <v>1</v>
       </c>
-      <c r="AC33" s="56">
+      <c r="AC33" s="57">
         <v>41901</v>
       </c>
-      <c r="AD33" s="61">
+      <c r="AD33" s="62">
         <v>42202</v>
       </c>
       <c r="AE33" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AF33" s="7"/>
       <c r="AG33" s="7"/>
       <c r="AH33" s="47"/>
       <c r="AI33" s="54"/>
       <c r="AJ33" s="54"/>
-      <c r="AK33" s="45"/>
+      <c r="AK33" s="55"/>
     </row>
-    <row r="34" spans="1:37" ht="65" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:37" ht="67.5" x14ac:dyDescent="0.15">
       <c r="A34" s="46" t="s">
+        <v>315</v>
+      </c>
+      <c r="B34" s="56" t="s">
         <v>316</v>
       </c>
-      <c r="B34" s="55"/>
       <c r="C34" s="48"/>
       <c r="D34" s="49">
         <v>2971232</v>
@@ -10882,9 +10835,7 @@
       <c r="Z34" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="AA34" s="47">
-        <v>0</v>
-      </c>
+      <c r="AA34" s="47"/>
       <c r="AB34" s="47">
         <v>1</v>
       </c>
@@ -10904,19 +10855,21 @@
       <c r="AH34" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="AI34" s="57" t="s">
+      <c r="AI34" s="58" t="s">
         <v>330</v>
       </c>
-      <c r="AJ34" s="57" t="s">
+      <c r="AJ34" s="58" t="s">
         <v>331</v>
       </c>
-      <c r="AK34" s="45"/>
+      <c r="AK34" s="79" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="35" spans="1:37" ht="65" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:37" ht="67.5" x14ac:dyDescent="0.15">
       <c r="A35" s="46" t="s">
-        <v>332</v>
-      </c>
-      <c r="B35" s="55"/>
+        <v>333</v>
+      </c>
+      <c r="B35" s="56"/>
       <c r="C35" s="48"/>
       <c r="D35" s="49">
         <v>2971257</v>
@@ -10942,34 +10895,34 @@
         <v>1</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L35" s="50" t="s">
         <v>44</v>
       </c>
       <c r="M35" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N35" s="50" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O35" s="7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P35" s="51" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q35" s="51" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="R35" s="50" t="s">
         <v>50</v>
       </c>
       <c r="S35" s="47" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="T35" s="52">
         <v>39114</v>
@@ -10987,7 +10940,7 @@
         <v>45748</v>
       </c>
       <c r="Y35" s="53" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Z35" s="53" t="s">
         <v>67</v>
@@ -10998,27 +10951,27 @@
       <c r="AB35" s="47">
         <v>1</v>
       </c>
-      <c r="AC35" s="56">
+      <c r="AC35" s="57">
         <v>41904</v>
       </c>
       <c r="AD35" s="47"/>
       <c r="AE35" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AF35" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG35" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AH35" s="47"/>
       <c r="AI35" s="54"/>
       <c r="AJ35" s="54"/>
-      <c r="AK35" s="45"/>
+      <c r="AK35" s="55"/>
     </row>
-    <row r="36" spans="1:37" ht="65" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:37" ht="67.5" x14ac:dyDescent="0.15">
       <c r="A36" s="46" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B36" s="7"/>
       <c r="C36" s="48"/>
@@ -11046,7 +10999,7 @@
         <v>9</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K36" s="7" t="s">
         <v>129</v>
@@ -11055,25 +11008,25 @@
         <v>44</v>
       </c>
       <c r="M36" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N36" s="50" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O36" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P36" s="51" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q36" s="51" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="R36" s="50" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="S36" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="T36" s="52">
         <v>39009</v>
@@ -11085,13 +11038,13 @@
         <v>39083</v>
       </c>
       <c r="W36" s="48" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X36" s="52">
         <v>45658</v>
       </c>
       <c r="Y36" s="53" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Z36" s="53" t="s">
         <v>67</v>
@@ -11107,26 +11060,26 @@
       </c>
       <c r="AD36" s="47"/>
       <c r="AE36" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AF36" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG36" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AH36" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="AI36" s="57" t="s">
         <v>359</v>
       </c>
+      <c r="AI36" s="58" t="s">
+        <v>360</v>
+      </c>
       <c r="AJ36" s="54"/>
-      <c r="AK36" s="45"/>
+      <c r="AK36" s="55"/>
     </row>
-    <row r="37" spans="1:37" ht="91" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:37" ht="94.5" x14ac:dyDescent="0.15">
       <c r="A37" s="46" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B37" s="7"/>
       <c r="C37" s="48"/>
@@ -11154,34 +11107,34 @@
         <v>9</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K37" s="7" t="s">
         <v>129</v>
       </c>
       <c r="L37" s="50" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M37" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N37" s="50" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O37" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P37" s="51" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q37" s="51" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="R37" s="50" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="S37" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="T37" s="48"/>
       <c r="U37" s="15">
@@ -11191,13 +11144,13 @@
         <v>38899</v>
       </c>
       <c r="W37" s="48" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="X37" s="52">
         <v>45474</v>
       </c>
       <c r="Y37" s="48" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Z37" s="53" t="s">
         <v>67</v>
@@ -11208,29 +11161,29 @@
       <c r="AB37" s="47">
         <v>1</v>
       </c>
-      <c r="AC37" s="56">
+      <c r="AC37" s="57">
         <v>41807</v>
       </c>
       <c r="AD37" s="47"/>
       <c r="AE37" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AF37" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="AG37" s="78" t="s">
         <v>367</v>
       </c>
+      <c r="AG37" s="79" t="s">
+        <v>368</v>
+      </c>
       <c r="AH37" s="7" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AI37" s="54"/>
       <c r="AJ37" s="54"/>
-      <c r="AK37" s="45"/>
+      <c r="AK37" s="55"/>
     </row>
-    <row r="38" spans="1:37" ht="65" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:37" ht="67.5" x14ac:dyDescent="0.15">
       <c r="A38" s="46" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B38" s="7"/>
       <c r="C38" s="48"/>
@@ -11258,7 +11211,7 @@
         <v>9</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K38" s="7" t="s">
         <v>129</v>
@@ -11267,25 +11220,25 @@
         <v>44</v>
       </c>
       <c r="M38" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N38" s="50" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O38" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P38" s="51" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q38" s="51" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="R38" s="50" t="s">
-        <v>259</v>
-      </c>
-      <c r="S38" s="79" t="s">
-        <v>369</v>
+        <v>258</v>
+      </c>
+      <c r="S38" s="80" t="s">
+        <v>370</v>
       </c>
       <c r="T38" s="52">
         <v>39009</v>
@@ -11297,13 +11250,13 @@
         <v>39083</v>
       </c>
       <c r="W38" s="48" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X38" s="52">
         <v>45658</v>
       </c>
       <c r="Y38" s="53" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Z38" s="53" t="s">
         <v>67</v>
@@ -11314,25 +11267,25 @@
       <c r="AB38" s="47">
         <v>1</v>
       </c>
-      <c r="AC38" s="56">
+      <c r="AC38" s="57">
         <v>41901</v>
       </c>
       <c r="AD38" s="47"/>
-      <c r="AE38" s="57" t="s">
-        <v>359</v>
+      <c r="AE38" s="58" t="s">
+        <v>360</v>
       </c>
       <c r="AF38" s="7" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG38" s="7"/>
       <c r="AH38" s="47"/>
       <c r="AI38" s="54"/>
       <c r="AJ38" s="54"/>
-      <c r="AK38" s="45"/>
+      <c r="AK38" s="55"/>
     </row>
-    <row r="39" spans="1:37" ht="65" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:37" ht="67.5" x14ac:dyDescent="0.15">
       <c r="A39" s="46" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B39" s="7"/>
       <c r="C39" s="48"/>
@@ -11360,7 +11313,7 @@
         <v>9</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K39" s="7" t="s">
         <v>129</v>
@@ -11369,25 +11322,25 @@
         <v>44</v>
       </c>
       <c r="M39" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N39" s="50" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O39" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P39" s="51" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q39" s="51" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="R39" s="50" t="s">
         <v>170</v>
       </c>
-      <c r="S39" s="80" t="s">
-        <v>372</v>
+      <c r="S39" s="81" t="s">
+        <v>373</v>
       </c>
       <c r="T39" s="52">
         <v>39009</v>
@@ -11399,13 +11352,13 @@
         <v>39083</v>
       </c>
       <c r="W39" s="48" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X39" s="52">
         <v>45658</v>
       </c>
       <c r="Y39" s="53" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Z39" s="53" t="s">
         <v>67</v>
@@ -11416,33 +11369,33 @@
       <c r="AB39" s="47">
         <v>1</v>
       </c>
-      <c r="AC39" s="56">
+      <c r="AC39" s="57">
         <v>41901</v>
       </c>
       <c r="AD39" s="47"/>
       <c r="AE39" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AF39" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG39" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AH39" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="AI39" s="57" t="s">
-        <v>359</v>
-      </c>
-      <c r="AJ39" s="57" t="s">
         <v>378</v>
       </c>
-      <c r="AK39" s="45"/>
+      <c r="AI39" s="58" t="s">
+        <v>360</v>
+      </c>
+      <c r="AJ39" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="AK39" s="55"/>
     </row>
-    <row r="40" spans="1:37" ht="65" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:37" ht="67.5" x14ac:dyDescent="0.15">
       <c r="A40" s="46" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B40" s="7"/>
       <c r="C40" s="48"/>
@@ -11470,7 +11423,7 @@
         <v>9</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K40" s="7" t="s">
         <v>129</v>
@@ -11479,25 +11432,25 @@
         <v>44</v>
       </c>
       <c r="M40" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N40" s="50" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O40" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P40" s="51" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q40" s="51" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="R40" s="50" t="s">
         <v>160</v>
       </c>
       <c r="S40" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="T40" s="52">
         <v>39009</v>
@@ -11509,13 +11462,13 @@
         <v>39083</v>
       </c>
       <c r="W40" s="48" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X40" s="52">
         <v>45658</v>
       </c>
       <c r="Y40" s="53" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Z40" s="53" t="s">
         <v>67</v>
@@ -11526,27 +11479,27 @@
       <c r="AB40" s="47">
         <v>1</v>
       </c>
-      <c r="AC40" s="56">
+      <c r="AC40" s="57">
         <v>41901</v>
       </c>
       <c r="AD40" s="47"/>
       <c r="AE40" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="AF40" s="57" t="s">
-        <v>359</v>
+        <v>382</v>
+      </c>
+      <c r="AF40" s="58" t="s">
+        <v>360</v>
       </c>
       <c r="AG40" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AH40" s="47"/>
-      <c r="AI40" s="57"/>
+      <c r="AI40" s="58"/>
       <c r="AJ40" s="54"/>
-      <c r="AK40" s="45"/>
+      <c r="AK40" s="55"/>
     </row>
-    <row r="41" spans="1:37" ht="78" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:37" ht="81" x14ac:dyDescent="0.15">
       <c r="A41" s="46" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B41" s="7"/>
       <c r="C41" s="48"/>
@@ -11574,34 +11527,34 @@
         <v>9</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K41" s="7" t="s">
         <v>129</v>
       </c>
       <c r="L41" s="50" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M41" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N41" s="50" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O41" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P41" s="51" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q41" s="51" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="R41" s="50" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="S41" s="7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="T41" s="48"/>
       <c r="U41" s="15">
@@ -11611,13 +11564,13 @@
         <v>38899</v>
       </c>
       <c r="W41" s="48" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="X41" s="52">
         <v>45474</v>
       </c>
       <c r="Y41" s="48" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Z41" s="53" t="s">
         <v>67</v>
@@ -11628,23 +11581,23 @@
       <c r="AB41" s="47">
         <v>1</v>
       </c>
-      <c r="AC41" s="56">
+      <c r="AC41" s="57">
         <v>41807</v>
       </c>
       <c r="AD41" s="47"/>
-      <c r="AE41" s="78" t="s">
-        <v>386</v>
+      <c r="AE41" s="79" t="s">
+        <v>387</v>
       </c>
       <c r="AF41" s="7"/>
       <c r="AG41" s="7"/>
       <c r="AH41" s="47"/>
       <c r="AI41" s="54"/>
       <c r="AJ41" s="54"/>
-      <c r="AK41" s="45"/>
+      <c r="AK41" s="55"/>
     </row>
-    <row r="42" spans="1:37" ht="65" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:37" ht="67.5" x14ac:dyDescent="0.15">
       <c r="A42" s="46" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B42" s="7"/>
       <c r="C42" s="48"/>
@@ -11672,7 +11625,7 @@
         <v>9</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K42" s="7" t="s">
         <v>129</v>
@@ -11681,25 +11634,25 @@
         <v>44</v>
       </c>
       <c r="M42" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N42" s="50" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O42" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P42" s="51" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q42" s="51" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="R42" s="50" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="S42" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="T42" s="52">
         <v>39009</v>
@@ -11711,13 +11664,13 @@
         <v>39083</v>
       </c>
       <c r="W42" s="48" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="X42" s="52">
         <v>45658</v>
       </c>
       <c r="Y42" s="53" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Z42" s="53" t="s">
         <v>67</v>
@@ -11728,25 +11681,25 @@
       <c r="AB42" s="47">
         <v>1</v>
       </c>
-      <c r="AC42" s="56">
+      <c r="AC42" s="57">
         <v>41901</v>
       </c>
       <c r="AD42" s="47"/>
-      <c r="AE42" s="57" t="s">
-        <v>359</v>
+      <c r="AE42" s="58" t="s">
+        <v>360</v>
       </c>
       <c r="AF42" s="7" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG42" s="7"/>
       <c r="AH42" s="47"/>
       <c r="AI42" s="54"/>
       <c r="AJ42" s="54"/>
-      <c r="AK42" s="45"/>
+      <c r="AK42" s="55"/>
     </row>
-    <row r="43" spans="1:37" ht="65" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:37" ht="67.5" x14ac:dyDescent="0.15">
       <c r="A43" s="46" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B43" s="7"/>
       <c r="C43" s="48"/>
@@ -11774,34 +11727,34 @@
         <v>9</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K43" s="7" t="s">
         <v>129</v>
       </c>
       <c r="L43" s="50" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M43" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N43" s="50" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O43" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P43" s="51" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q43" s="51" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="R43" s="50" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="S43" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="T43" s="48"/>
       <c r="U43" s="15">
@@ -11811,13 +11764,13 @@
         <v>38899</v>
       </c>
       <c r="W43" s="48" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="X43" s="52">
         <v>45474</v>
       </c>
-      <c r="Y43" s="58" t="s">
-        <v>391</v>
+      <c r="Y43" s="59" t="s">
+        <v>392</v>
       </c>
       <c r="Z43" s="53" t="s">
         <v>67</v>
@@ -11833,24 +11786,24 @@
       </c>
       <c r="AD43" s="47"/>
       <c r="AE43" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="AF43" s="78" t="s">
         <v>393</v>
       </c>
+      <c r="AF43" s="79" t="s">
+        <v>394</v>
+      </c>
       <c r="AG43" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AH43" s="7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AI43" s="54"/>
       <c r="AJ43" s="54"/>
-      <c r="AK43" s="45"/>
+      <c r="AK43" s="55"/>
     </row>
-    <row r="44" spans="1:37" ht="65" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:37" ht="67.5" x14ac:dyDescent="0.15">
       <c r="A44" s="46" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B44" s="7"/>
       <c r="C44" s="48"/>
@@ -11878,7 +11831,7 @@
         <v>9</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K44" s="7" t="s">
         <v>129</v>
@@ -11887,25 +11840,25 @@
         <v>44</v>
       </c>
       <c r="M44" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N44" s="50" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O44" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P44" s="51" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q44" s="51" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="R44" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="S44" s="80" t="s">
-        <v>396</v>
+      <c r="S44" s="81" t="s">
+        <v>397</v>
       </c>
       <c r="T44" s="52">
         <v>39009</v>
@@ -11923,7 +11876,7 @@
         <v>45658</v>
       </c>
       <c r="Y44" s="53" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Z44" s="53" t="s">
         <v>67</v>
@@ -11934,29 +11887,29 @@
       <c r="AB44" s="47">
         <v>1</v>
       </c>
-      <c r="AC44" s="56">
+      <c r="AC44" s="57">
         <v>41901</v>
       </c>
       <c r="AD44" s="47"/>
       <c r="AE44" s="7" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AF44" s="7" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG44" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AH44" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AI44" s="54"/>
       <c r="AJ44" s="54"/>
-      <c r="AK44" s="45"/>
+      <c r="AK44" s="55"/>
     </row>
-    <row r="45" spans="1:37" ht="52" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:37" ht="54" x14ac:dyDescent="0.15">
       <c r="A45" s="46" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B45" s="47"/>
       <c r="C45" s="48"/>
@@ -11984,7 +11937,7 @@
         <v>2</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K45" s="7" t="s">
         <v>156</v>
@@ -11993,10 +11946,10 @@
         <v>44</v>
       </c>
       <c r="M45" s="7" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N45" s="50" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O45" s="7" t="s">
         <v>159</v>
@@ -12005,13 +11958,13 @@
         <v>156</v>
       </c>
       <c r="Q45" s="51" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="R45" s="50" t="s">
         <v>170</v>
       </c>
       <c r="S45" s="47" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="T45" s="52">
         <v>38992</v>
@@ -12029,7 +11982,7 @@
         <v>45658</v>
       </c>
       <c r="Y45" s="53" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Z45" s="53" t="s">
         <v>67</v>
@@ -12045,20 +11998,20 @@
       </c>
       <c r="AD45" s="47"/>
       <c r="AE45" s="7" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AF45" s="7" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG45" s="7"/>
       <c r="AH45" s="47"/>
       <c r="AI45" s="54"/>
       <c r="AJ45" s="54"/>
-      <c r="AK45" s="45"/>
+      <c r="AK45" s="55"/>
     </row>
-    <row r="46" spans="1:37" ht="52" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:37" ht="54" x14ac:dyDescent="0.15">
       <c r="A46" s="46" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B46" s="47"/>
       <c r="C46" s="48"/>
@@ -12086,7 +12039,7 @@
         <v>2</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K46" s="7" t="s">
         <v>156</v>
@@ -12095,10 +12048,10 @@
         <v>44</v>
       </c>
       <c r="M46" s="7" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N46" s="50" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O46" s="7" t="s">
         <v>159</v>
@@ -12107,13 +12060,13 @@
         <v>156</v>
       </c>
       <c r="Q46" s="51" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="R46" s="50" t="s">
         <v>160</v>
       </c>
       <c r="S46" s="47" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="T46" s="52">
         <v>38992</v>
@@ -12131,7 +12084,7 @@
         <v>45658</v>
       </c>
       <c r="Y46" s="53" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Z46" s="53" t="s">
         <v>67</v>
@@ -12142,23 +12095,23 @@
       <c r="AB46" s="47">
         <v>1</v>
       </c>
-      <c r="AC46" s="56">
+      <c r="AC46" s="57">
         <v>41901</v>
       </c>
       <c r="AD46" s="47"/>
       <c r="AE46" s="7" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AF46" s="7"/>
       <c r="AG46" s="7"/>
       <c r="AH46" s="47"/>
       <c r="AI46" s="54"/>
       <c r="AJ46" s="54"/>
-      <c r="AK46" s="45"/>
+      <c r="AK46" s="55"/>
     </row>
-    <row r="47" spans="1:37" ht="78" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:37" ht="81" x14ac:dyDescent="0.15">
       <c r="A47" s="46" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B47" s="47"/>
       <c r="C47" s="48"/>
@@ -12186,34 +12139,34 @@
         <v>1</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K47" s="7" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L47" s="50" t="s">
         <v>44</v>
       </c>
       <c r="M47" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N47" s="50" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O47" s="7" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P47" s="51" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q47" s="51" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="R47" s="50" t="s">
         <v>50</v>
       </c>
       <c r="S47" s="47" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="T47" s="52">
         <v>39016</v>
@@ -12231,7 +12184,7 @@
         <v>45658</v>
       </c>
       <c r="Y47" s="53" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Z47" s="53" t="s">
         <v>67</v>
@@ -12242,35 +12195,35 @@
       <c r="AB47" s="47">
         <v>1</v>
       </c>
-      <c r="AC47" s="56">
+      <c r="AC47" s="57">
         <v>41901</v>
       </c>
       <c r="AD47" s="47"/>
       <c r="AE47" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AF47" s="7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG47" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AH47" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AI47" s="7" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AJ47" s="54"/>
-      <c r="AK47" s="45"/>
+      <c r="AK47" s="55"/>
     </row>
-    <row r="48" spans="1:37" s="86" customFormat="1" ht="39" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="81" t="s">
-        <v>427</v>
-      </c>
-      <c r="B48" s="81"/>
-      <c r="C48" s="82"/>
-      <c r="D48" s="81">
+    <row r="48" spans="1:37" s="87" customFormat="1" ht="40.5" x14ac:dyDescent="0.15">
+      <c r="A48" s="82" t="s">
+        <v>428</v>
+      </c>
+      <c r="B48" s="82"/>
+      <c r="C48" s="83"/>
+      <c r="D48" s="82">
         <v>2971018</v>
       </c>
       <c r="E48" s="47">
@@ -12293,35 +12246,35 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="J48" s="78" t="s">
-        <v>428</v>
-      </c>
-      <c r="K48" s="78" t="s">
+      <c r="J48" s="79" t="s">
         <v>429</v>
       </c>
-      <c r="L48" s="78" t="s">
+      <c r="K48" s="79" t="s">
+        <v>430</v>
+      </c>
+      <c r="L48" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="M48" s="78" t="s">
+      <c r="M48" s="79" t="s">
+        <v>431</v>
+      </c>
+      <c r="N48" s="79" t="s">
+        <v>432</v>
+      </c>
+      <c r="O48" s="79" t="s">
+        <v>433</v>
+      </c>
+      <c r="P48" s="84" t="s">
         <v>430</v>
       </c>
-      <c r="N48" s="78" t="s">
+      <c r="Q48" s="84" t="s">
         <v>431</v>
       </c>
-      <c r="O48" s="78" t="s">
-        <v>432</v>
-      </c>
-      <c r="P48" s="83" t="s">
-        <v>429</v>
-      </c>
-      <c r="Q48" s="83" t="s">
-        <v>430</v>
-      </c>
-      <c r="R48" s="81" t="s">
+      <c r="R48" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="S48" s="81" t="s">
-        <v>433</v>
+      <c r="S48" s="82" t="s">
+        <v>434</v>
       </c>
       <c r="T48" s="52">
         <v>42241</v>
@@ -12332,43 +12285,43 @@
       <c r="V48" s="52">
         <v>42278</v>
       </c>
-      <c r="W48" s="82" t="s">
-        <v>434</v>
-      </c>
-      <c r="X48" s="84">
+      <c r="W48" s="83" t="s">
+        <v>435</v>
+      </c>
+      <c r="X48" s="85">
         <v>44470</v>
       </c>
-      <c r="Y48" s="67" t="s">
-        <v>435</v>
-      </c>
-      <c r="Z48" s="82" t="s">
+      <c r="Y48" s="68" t="s">
+        <v>436</v>
+      </c>
+      <c r="Z48" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="AA48" s="81"/>
-      <c r="AB48" s="81">
+      <c r="AA48" s="82"/>
+      <c r="AB48" s="82">
         <v>1</v>
       </c>
-      <c r="AC48" s="81">
+      <c r="AC48" s="82">
         <v>42710</v>
       </c>
-      <c r="AD48" s="81"/>
+      <c r="AD48" s="82"/>
       <c r="AE48" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="AF48" s="81"/>
-      <c r="AG48" s="81"/>
-      <c r="AH48" s="81"/>
-      <c r="AI48" s="81"/>
-      <c r="AJ48" s="85"/>
-      <c r="AK48" s="81"/>
+        <v>437</v>
+      </c>
+      <c r="AF48" s="82"/>
+      <c r="AG48" s="82"/>
+      <c r="AH48" s="82"/>
+      <c r="AI48" s="82"/>
+      <c r="AJ48" s="86"/>
+      <c r="AK48" s="82"/>
     </row>
-    <row r="49" spans="1:37" ht="39" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:37" ht="40.5" x14ac:dyDescent="0.15">
       <c r="A49" s="46" t="s">
-        <v>437</v>
-      </c>
-      <c r="B49" s="82"/>
-      <c r="C49" s="82"/>
-      <c r="D49" s="81">
+        <v>438</v>
+      </c>
+      <c r="B49" s="83"/>
+      <c r="C49" s="83"/>
+      <c r="D49" s="82">
         <v>2930097</v>
       </c>
       <c r="E49" s="47">
@@ -12391,37 +12344,37 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="J49" s="78" t="s">
-        <v>438</v>
-      </c>
-      <c r="K49" s="78" t="s">
+      <c r="J49" s="79" t="s">
         <v>439</v>
       </c>
-      <c r="L49" s="78" t="s">
+      <c r="K49" s="79" t="s">
+        <v>440</v>
+      </c>
+      <c r="L49" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="M49" s="78" t="s">
-        <v>440</v>
-      </c>
-      <c r="N49" s="78" t="s">
+      <c r="M49" s="79" t="s">
         <v>441</v>
       </c>
-      <c r="O49" s="78" t="s">
+      <c r="N49" s="79" t="s">
         <v>442</v>
       </c>
-      <c r="P49" s="83" t="s">
+      <c r="O49" s="79" t="s">
         <v>443</v>
       </c>
-      <c r="Q49" s="87" t="s">
+      <c r="P49" s="84" t="s">
         <v>444</v>
       </c>
-      <c r="R49" s="81" t="s">
+      <c r="Q49" s="88" t="s">
         <v>445</v>
       </c>
-      <c r="S49" s="81" t="s">
+      <c r="R49" s="82" t="s">
         <v>446</v>
       </c>
-      <c r="T49" s="84">
+      <c r="S49" s="82" t="s">
+        <v>447</v>
+      </c>
+      <c r="T49" s="85">
         <v>42513</v>
       </c>
       <c r="U49" s="15">
@@ -12430,43 +12383,43 @@
       <c r="V49" s="52">
         <v>42552</v>
       </c>
-      <c r="W49" s="82" t="s">
-        <v>447</v>
-      </c>
-      <c r="X49" s="84">
+      <c r="W49" s="83" t="s">
+        <v>448</v>
+      </c>
+      <c r="X49" s="85">
         <v>44743</v>
       </c>
-      <c r="Y49" s="67" t="s">
-        <v>448</v>
-      </c>
-      <c r="Z49" s="82" t="s">
+      <c r="Y49" s="68" t="s">
+        <v>449</v>
+      </c>
+      <c r="Z49" s="83" t="s">
         <v>17</v>
       </c>
-      <c r="AA49" s="81"/>
-      <c r="AB49" s="81">
+      <c r="AA49" s="82"/>
+      <c r="AB49" s="82">
         <v>1</v>
       </c>
-      <c r="AC49" s="81">
+      <c r="AC49" s="82">
         <v>42807</v>
       </c>
-      <c r="AD49" s="81"/>
+      <c r="AD49" s="82"/>
       <c r="AE49" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="AF49" s="81"/>
-      <c r="AG49" s="81"/>
-      <c r="AH49" s="81"/>
-      <c r="AI49" s="81"/>
-      <c r="AJ49" s="85"/>
-      <c r="AK49" s="45"/>
+        <v>450</v>
+      </c>
+      <c r="AF49" s="82"/>
+      <c r="AG49" s="82"/>
+      <c r="AH49" s="82"/>
+      <c r="AI49" s="82"/>
+      <c r="AJ49" s="86"/>
+      <c r="AK49" s="55"/>
     </row>
-    <row r="50" spans="1:37" s="86" customFormat="1" ht="52" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="81" t="s">
-        <v>450</v>
-      </c>
-      <c r="B50" s="88"/>
-      <c r="C50" s="82"/>
-      <c r="D50" s="81">
+    <row r="50" spans="1:37" s="87" customFormat="1" ht="54" x14ac:dyDescent="0.15">
+      <c r="A50" s="82" t="s">
+        <v>451</v>
+      </c>
+      <c r="B50" s="89"/>
+      <c r="C50" s="83"/>
+      <c r="D50" s="82">
         <v>2947430</v>
       </c>
       <c r="E50" s="47">
@@ -12489,37 +12442,37 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="J50" s="78" t="s">
-        <v>451</v>
-      </c>
-      <c r="K50" s="78" t="s">
+      <c r="J50" s="79" t="s">
         <v>452</v>
       </c>
-      <c r="L50" s="78" t="s">
+      <c r="K50" s="79" t="s">
+        <v>453</v>
+      </c>
+      <c r="L50" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="M50" s="78" t="s">
-        <v>453</v>
-      </c>
-      <c r="N50" s="78" t="s">
+      <c r="M50" s="79" t="s">
         <v>454</v>
       </c>
-      <c r="O50" s="78" t="s">
+      <c r="N50" s="79" t="s">
         <v>455</v>
       </c>
-      <c r="P50" s="83" t="s">
+      <c r="O50" s="79" t="s">
         <v>456</v>
       </c>
-      <c r="Q50" s="87" t="s">
+      <c r="P50" s="84" t="s">
         <v>457</v>
       </c>
+      <c r="Q50" s="88" t="s">
+        <v>458</v>
+      </c>
       <c r="R50" s="50" t="s">
-        <v>224</v>
-      </c>
-      <c r="S50" s="81" t="s">
-        <v>455</v>
-      </c>
-      <c r="T50" s="84">
+        <v>223</v>
+      </c>
+      <c r="S50" s="82" t="s">
+        <v>456</v>
+      </c>
+      <c r="T50" s="85">
         <v>42773</v>
       </c>
       <c r="U50" s="15">
@@ -12528,45 +12481,45 @@
       <c r="V50" s="52">
         <v>42826</v>
       </c>
-      <c r="W50" s="82" t="s">
-        <v>458</v>
-      </c>
-      <c r="X50" s="89">
+      <c r="W50" s="83" t="s">
+        <v>459</v>
+      </c>
+      <c r="X50" s="90">
         <v>45017</v>
       </c>
-      <c r="Y50" s="82" t="s">
-        <v>459</v>
+      <c r="Y50" s="83" t="s">
+        <v>460</v>
       </c>
       <c r="Z50" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="AA50" s="81">
+      <c r="AA50" s="82">
         <v>1</v>
       </c>
-      <c r="AB50" s="81">
+      <c r="AB50" s="82">
         <v>1</v>
       </c>
-      <c r="AC50" s="81">
+      <c r="AC50" s="82">
         <v>42904</v>
       </c>
-      <c r="AD50" s="81"/>
-      <c r="AE50" s="78" t="s">
-        <v>460</v>
-      </c>
-      <c r="AF50" s="81"/>
-      <c r="AG50" s="81"/>
-      <c r="AH50" s="81"/>
-      <c r="AI50" s="81"/>
-      <c r="AJ50" s="85"/>
-      <c r="AK50" s="81"/>
+      <c r="AD50" s="82"/>
+      <c r="AE50" s="79" t="s">
+        <v>461</v>
+      </c>
+      <c r="AF50" s="82"/>
+      <c r="AG50" s="82"/>
+      <c r="AH50" s="82"/>
+      <c r="AI50" s="82"/>
+      <c r="AJ50" s="86"/>
+      <c r="AK50" s="82"/>
     </row>
-    <row r="51" spans="1:37" ht="65" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="81" t="s">
-        <v>461</v>
-      </c>
-      <c r="B51" s="81"/>
-      <c r="C51" s="82"/>
-      <c r="D51" s="81">
+    <row r="51" spans="1:37" ht="67.5" x14ac:dyDescent="0.15">
+      <c r="A51" s="82" t="s">
+        <v>462</v>
+      </c>
+      <c r="B51" s="82"/>
+      <c r="C51" s="83"/>
+      <c r="D51" s="82">
         <v>2930477</v>
       </c>
       <c r="E51" s="47">
@@ -12589,37 +12542,37 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J51" s="78" t="s">
-        <v>462</v>
-      </c>
-      <c r="K51" s="78" t="s">
+      <c r="J51" s="79" t="s">
+        <v>463</v>
+      </c>
+      <c r="K51" s="79" t="s">
         <v>123</v>
       </c>
-      <c r="L51" s="78" t="s">
+      <c r="L51" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="M51" s="78" t="s">
-        <v>463</v>
-      </c>
-      <c r="N51" s="78" t="s">
+      <c r="M51" s="79" t="s">
         <v>464</v>
       </c>
-      <c r="O51" s="78" t="s">
+      <c r="N51" s="79" t="s">
         <v>465</v>
       </c>
-      <c r="P51" s="83" t="s">
+      <c r="O51" s="79" t="s">
         <v>466</v>
       </c>
-      <c r="Q51" s="87" t="s">
+      <c r="P51" s="84" t="s">
         <v>467</v>
       </c>
+      <c r="Q51" s="88" t="s">
+        <v>468</v>
+      </c>
       <c r="R51" s="50" t="s">
-        <v>468</v>
-      </c>
-      <c r="S51" s="78" t="s">
         <v>469</v>
       </c>
-      <c r="T51" s="84">
+      <c r="S51" s="79" t="s">
+        <v>470</v>
+      </c>
+      <c r="T51" s="85">
         <v>44140</v>
       </c>
       <c r="U51" s="15">
@@ -12628,47 +12581,47 @@
       <c r="V51" s="52">
         <v>43922</v>
       </c>
-      <c r="W51" s="82" t="s">
-        <v>470</v>
-      </c>
-      <c r="X51" s="89">
+      <c r="W51" s="83" t="s">
+        <v>471</v>
+      </c>
+      <c r="X51" s="90">
         <v>46113</v>
       </c>
-      <c r="Y51" s="82" t="s">
-        <v>471</v>
+      <c r="Y51" s="83" t="s">
+        <v>472</v>
       </c>
       <c r="Z51" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="AA51" s="81">
+      <c r="AA51" s="82">
         <v>1</v>
       </c>
-      <c r="AB51" s="81">
+      <c r="AB51" s="82">
         <v>1</v>
       </c>
-      <c r="AC51" s="81">
+      <c r="AC51" s="82">
         <v>50204</v>
       </c>
-      <c r="AD51" s="81"/>
-      <c r="AE51" s="78" t="s">
-        <v>472</v>
-      </c>
-      <c r="AF51" s="78" t="s">
+      <c r="AD51" s="82"/>
+      <c r="AE51" s="79" t="s">
         <v>473</v>
       </c>
-      <c r="AG51" s="81"/>
-      <c r="AH51" s="81"/>
-      <c r="AI51" s="81"/>
-      <c r="AJ51" s="85"/>
-      <c r="AK51" s="45"/>
+      <c r="AF51" s="79" t="s">
+        <v>474</v>
+      </c>
+      <c r="AG51" s="82"/>
+      <c r="AH51" s="82"/>
+      <c r="AI51" s="82"/>
+      <c r="AJ51" s="86"/>
+      <c r="AK51" s="55"/>
     </row>
-    <row r="52" spans="1:37" s="86" customFormat="1" ht="78" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="90" t="s">
-        <v>474</v>
-      </c>
-      <c r="B52" s="88"/>
-      <c r="C52" s="82"/>
-      <c r="D52" s="81">
+    <row r="52" spans="1:37" s="87" customFormat="1" ht="81" x14ac:dyDescent="0.15">
+      <c r="A52" s="91" t="s">
+        <v>475</v>
+      </c>
+      <c r="B52" s="89"/>
+      <c r="C52" s="83"/>
+      <c r="D52" s="82">
         <v>2930766</v>
       </c>
       <c r="E52" s="47">
@@ -12691,37 +12644,37 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J52" s="78" t="s">
-        <v>475</v>
-      </c>
-      <c r="K52" s="78" t="s">
+      <c r="J52" s="79" t="s">
         <v>476</v>
       </c>
-      <c r="L52" s="78" t="s">
+      <c r="K52" s="79" t="s">
+        <v>477</v>
+      </c>
+      <c r="L52" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="M52" s="78" t="s">
-        <v>477</v>
-      </c>
-      <c r="N52" s="78" t="s">
+      <c r="M52" s="79" t="s">
         <v>478</v>
       </c>
-      <c r="O52" s="78" t="s">
+      <c r="N52" s="79" t="s">
         <v>479</v>
       </c>
-      <c r="P52" s="83" t="s">
+      <c r="O52" s="79" t="s">
         <v>480</v>
       </c>
-      <c r="Q52" s="87" t="s">
+      <c r="P52" s="84" t="s">
         <v>481</v>
       </c>
+      <c r="Q52" s="88" t="s">
+        <v>482</v>
+      </c>
       <c r="R52" s="50" t="s">
-        <v>468</v>
-      </c>
-      <c r="S52" s="81" t="s">
+        <v>469</v>
+      </c>
+      <c r="S52" s="82" t="s">
         <v>135</v>
       </c>
-      <c r="T52" s="84">
+      <c r="T52" s="85">
         <v>44586</v>
       </c>
       <c r="U52" s="15">
@@ -12730,96 +12683,96 @@
       <c r="V52" s="15">
         <v>44652</v>
       </c>
-      <c r="W52" s="82" t="s">
-        <v>482</v>
-      </c>
-      <c r="X52" s="82"/>
-      <c r="Y52" s="82"/>
+      <c r="W52" s="83" t="s">
+        <v>483</v>
+      </c>
+      <c r="X52" s="83"/>
+      <c r="Y52" s="83"/>
       <c r="Z52" s="53" t="s">
-        <v>483</v>
-      </c>
-      <c r="AA52" s="81"/>
-      <c r="AB52" s="81">
+        <v>484</v>
+      </c>
+      <c r="AA52" s="82"/>
+      <c r="AB52" s="82">
         <v>1</v>
       </c>
-      <c r="AC52" s="81">
+      <c r="AC52" s="82">
         <v>50404</v>
       </c>
-      <c r="AD52" s="81"/>
-      <c r="AE52" s="78" t="s">
-        <v>484</v>
-      </c>
-      <c r="AF52" s="57" t="s">
+      <c r="AD52" s="82"/>
+      <c r="AE52" s="79" t="s">
         <v>485</v>
       </c>
-      <c r="AG52" s="81"/>
-      <c r="AH52" s="81"/>
-      <c r="AI52" s="81"/>
-      <c r="AJ52" s="85"/>
-      <c r="AK52" s="81"/>
+      <c r="AF52" s="58" t="s">
+        <v>486</v>
+      </c>
+      <c r="AG52" s="82"/>
+      <c r="AH52" s="82"/>
+      <c r="AI52" s="82"/>
+      <c r="AJ52" s="86"/>
+      <c r="AK52" s="82"/>
     </row>
-    <row r="53" spans="1:37" ht="26" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="90" t="s">
-        <v>486</v>
-      </c>
-      <c r="B53" s="81"/>
+    <row r="53" spans="1:37" ht="27" x14ac:dyDescent="0.15">
+      <c r="A53" s="91" t="s">
+        <v>487</v>
+      </c>
+      <c r="B53" s="82"/>
       <c r="C53" s="48" t="s">
         <v>154</v>
       </c>
-      <c r="D53" s="81">
+      <c r="D53" s="82">
         <v>2971265</v>
       </c>
-      <c r="E53" s="91">
+      <c r="E53" s="92">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="F53" s="92" t="str">
+      <c r="F53" s="93" t="str">
         <f t="shared" si="1"/>
         <v>医科</v>
       </c>
-      <c r="G53" s="92" t="str">
+      <c r="G53" s="93" t="str">
         <f t="shared" si="2"/>
         <v>1312971265</v>
       </c>
-      <c r="H53" s="92" t="str">
+      <c r="H53" s="93" t="str">
         <f t="shared" si="3"/>
         <v>　</v>
       </c>
-      <c r="I53" s="91">
+      <c r="I53" s="92">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J53" s="93" t="s">
-        <v>487</v>
-      </c>
-      <c r="K53" s="78" t="s">
+      <c r="J53" s="94" t="s">
+        <v>488</v>
+      </c>
+      <c r="K53" s="79" t="s">
         <v>114</v>
       </c>
-      <c r="L53" s="78" t="s">
+      <c r="L53" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="M53" s="78" t="s">
-        <v>488</v>
-      </c>
-      <c r="N53" s="78" t="s">
+      <c r="M53" s="79" t="s">
         <v>489</v>
       </c>
-      <c r="O53" s="78" t="s">
+      <c r="N53" s="79" t="s">
         <v>490</v>
       </c>
-      <c r="P53" s="83" t="s">
+      <c r="O53" s="79" t="s">
         <v>491</v>
       </c>
-      <c r="Q53" s="87" t="s">
+      <c r="P53" s="84" t="s">
         <v>492</v>
       </c>
+      <c r="Q53" s="88" t="s">
+        <v>493</v>
+      </c>
       <c r="R53" s="50" t="s">
-        <v>468</v>
-      </c>
-      <c r="S53" s="78" t="s">
-        <v>493</v>
-      </c>
-      <c r="T53" s="84">
+        <v>469</v>
+      </c>
+      <c r="S53" s="79" t="s">
+        <v>494</v>
+      </c>
+      <c r="T53" s="85">
         <v>44602</v>
       </c>
       <c r="U53" s="15">
@@ -12828,41 +12781,41 @@
       <c r="V53" s="15">
         <v>44652</v>
       </c>
-      <c r="W53" s="82" t="s">
-        <v>494</v>
-      </c>
-      <c r="X53" s="82"/>
-      <c r="Y53" s="82"/>
+      <c r="W53" s="83" t="s">
+        <v>495</v>
+      </c>
+      <c r="X53" s="83"/>
+      <c r="Y53" s="83"/>
       <c r="Z53" s="53" t="s">
-        <v>483</v>
-      </c>
-      <c r="AA53" s="81"/>
-      <c r="AB53" s="81">
+        <v>484</v>
+      </c>
+      <c r="AA53" s="82"/>
+      <c r="AB53" s="82">
         <v>1</v>
       </c>
-      <c r="AC53" s="81">
+      <c r="AC53" s="82">
         <v>50404</v>
       </c>
-      <c r="AD53" s="94">
+      <c r="AD53" s="95">
         <v>50605</v>
       </c>
-      <c r="AE53" s="78" t="s">
-        <v>495</v>
-      </c>
-      <c r="AF53" s="81"/>
-      <c r="AG53" s="81"/>
-      <c r="AH53" s="81"/>
-      <c r="AI53" s="81"/>
-      <c r="AJ53" s="85"/>
-      <c r="AK53" s="45"/>
+      <c r="AE53" s="79" t="s">
+        <v>496</v>
+      </c>
+      <c r="AF53" s="82"/>
+      <c r="AG53" s="82"/>
+      <c r="AH53" s="82"/>
+      <c r="AI53" s="82"/>
+      <c r="AJ53" s="86"/>
+      <c r="AK53" s="55"/>
     </row>
-    <row r="54" spans="1:37" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:37" x14ac:dyDescent="0.15">
       <c r="AF54" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AJ54" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:AK54" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="24">
     <mergeCell ref="AF2:AF3"/>
     <mergeCell ref="AG2:AG3"/>
@@ -12892,7 +12845,7 @@
   <phoneticPr fontId="3"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062992" bottom="0.15748031496062992" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="34" fitToHeight="2" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;P / &amp;N ページ</oddFooter>
   </headerFooter>
